--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_air_transport.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09778676894003105</v>
+        <v>0.09762719540215098</v>
       </c>
       <c r="C2">
-        <v>2392.893480531276</v>
+        <v>2374.51217956224</v>
       </c>
       <c r="D2">
-        <v>1918.993480531276</v>
+        <v>1923.922819485664</v>
       </c>
       <c r="E2">
-        <v>-1785.263992342367</v>
+        <v>-1761.953352418943</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23.31063992342367</v>
       </c>
       <c r="G2">
         <v>473.9</v>
@@ -1451,28 +1451,28 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.17252518814821</v>
       </c>
       <c r="N2">
-        <v>38.59999999999999</v>
+        <v>37.42747481185178</v>
       </c>
       <c r="O2">
-        <v>7.719999999999999</v>
+        <v>7.485494962370357</v>
       </c>
       <c r="P2">
-        <v>30.88</v>
+        <v>29.94197984948142</v>
       </c>
       <c r="Q2">
-        <v>217.08</v>
+        <v>216.1419798494814</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09778676894003105</v>
+        <v>0.09820686404257675</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8107175193586469</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>32.92040153180986</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09762719540215098</v>
+        <v>0.09746762186427092</v>
       </c>
       <c r="C3">
-        <v>2374.51217956224</v>
+        <v>2356.156267901745</v>
       </c>
       <c r="D3">
-        <v>1923.922819485664</v>
+        <v>1928.877547748592</v>
       </c>
       <c r="E3">
-        <v>-1761.953352418943</v>
+        <v>-1738.64271249552</v>
       </c>
       <c r="F3">
-        <v>23.31063992342367</v>
+        <v>46.62127984684734</v>
       </c>
       <c r="G3">
         <v>473.9</v>
@@ -1533,28 +1533,28 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M3">
-        <v>1.17252518814821</v>
+        <v>2.345050376296421</v>
       </c>
       <c r="N3">
-        <v>37.42747481185178</v>
+        <v>36.25494962370357</v>
       </c>
       <c r="O3">
-        <v>7.485494962370357</v>
+        <v>7.250989924740715</v>
       </c>
       <c r="P3">
-        <v>29.94197984948142</v>
+        <v>29.00395969896286</v>
       </c>
       <c r="Q3">
-        <v>216.1419798494814</v>
+        <v>215.2039596989628</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09820686404257675</v>
+        <v>0.09863553251456217</v>
       </c>
       <c r="T3">
-        <v>0.8107175193586469</v>
+        <v>0.8173488842873504</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>32.92040153180986</v>
+        <v>16.46020076590493</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09746762186427092</v>
+        <v>0.09734404832639085</v>
       </c>
       <c r="C4">
-        <v>2356.156267901745</v>
+        <v>2336.700131535584</v>
       </c>
       <c r="D4">
-        <v>1928.877547748592</v>
+        <v>1932.732051305855</v>
       </c>
       <c r="E4">
-        <v>-1738.64271249552</v>
+        <v>-1715.332072572096</v>
       </c>
       <c r="F4">
-        <v>46.62127984684734</v>
+        <v>69.93191977027101</v>
       </c>
       <c r="G4">
         <v>473.9</v>
@@ -1615,45 +1615,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M4">
-        <v>2.345050376296421</v>
+        <v>3.622473444100038</v>
       </c>
       <c r="N4">
-        <v>36.25494962370357</v>
+        <v>34.97752655589996</v>
       </c>
       <c r="O4">
-        <v>7.250989924740715</v>
+        <v>6.995505311179992</v>
       </c>
       <c r="P4">
-        <v>29.00395969896286</v>
+        <v>27.98202124471997</v>
       </c>
       <c r="Q4">
-        <v>215.2039596989628</v>
+        <v>214.1820212447199</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09863553251456217</v>
+        <v>0.09907303951174315</v>
       </c>
       <c r="T4">
-        <v>0.8173488842873504</v>
+        <v>0.8241169783898415</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.46020076590493</v>
+        <v>10.65570268371966</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09734404832639085</v>
+        <v>0.09725087478851081</v>
       </c>
       <c r="C5">
-        <v>2336.700131535584</v>
+        <v>2316.305960840819</v>
       </c>
       <c r="D5">
-        <v>1932.732051305855</v>
+        <v>1935.648520534514</v>
       </c>
       <c r="E5">
-        <v>-1715.332072572096</v>
+        <v>-1692.021432648673</v>
       </c>
       <c r="F5">
-        <v>69.93191977027101</v>
+        <v>93.24255969369467</v>
       </c>
       <c r="G5">
         <v>473.9</v>
@@ -1697,45 +1697,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M5">
-        <v>3.622473444100038</v>
+        <v>4.988476943612665</v>
       </c>
       <c r="N5">
-        <v>34.97752655589996</v>
+        <v>33.61152305638733</v>
       </c>
       <c r="O5">
-        <v>6.995505311179992</v>
+        <v>6.722304611277465</v>
       </c>
       <c r="P5">
-        <v>27.98202124471997</v>
+        <v>26.88921844510986</v>
       </c>
       <c r="Q5">
-        <v>214.1820212447199</v>
+        <v>213.0892184451099</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09907303951174315</v>
+        <v>0.09951966123803209</v>
       </c>
       <c r="T5">
-        <v>0.8241169783898415</v>
+        <v>0.8310260744528014</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.65570268371966</v>
+        <v>7.737832696495495</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09725087478851081</v>
+        <v>0.09718890125063073</v>
       </c>
       <c r="C6">
-        <v>2316.305960840819</v>
+        <v>2294.940063253092</v>
       </c>
       <c r="D6">
-        <v>1935.648520534514</v>
+        <v>1937.593262870211</v>
       </c>
       <c r="E6">
-        <v>-1692.021432648673</v>
+        <v>-1668.710792725249</v>
       </c>
       <c r="F6">
-        <v>93.24255969369467</v>
+        <v>116.5531996171184</v>
       </c>
       <c r="G6">
         <v>473.9</v>
@@ -1779,45 +1779,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M6">
-        <v>4.988476943612665</v>
+        <v>6.445391938826645</v>
       </c>
       <c r="N6">
-        <v>33.61152305638733</v>
+        <v>32.15460806117335</v>
       </c>
       <c r="O6">
-        <v>6.722304611277465</v>
+        <v>6.43092161223467</v>
       </c>
       <c r="P6">
-        <v>26.88921844510986</v>
+        <v>25.72368644893868</v>
       </c>
       <c r="Q6">
-        <v>213.0892184451099</v>
+        <v>211.9236864489387</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09951966123803209</v>
+        <v>0.09997568552697972</v>
       </c>
       <c r="T6">
-        <v>0.8310260744528014</v>
+        <v>0.8380806251697182</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.0428</v>
+        <v>0.04424</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.737832696495495</v>
+        <v>5.988774672875356</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09718890125063073</v>
+        <v>0.09706932771275067</v>
       </c>
       <c r="C7">
-        <v>2294.940063253092</v>
+        <v>2275.392730502037</v>
       </c>
       <c r="D7">
-        <v>1937.593262870211</v>
+        <v>1941.356570042579</v>
       </c>
       <c r="E7">
-        <v>-1668.710792725249</v>
+        <v>-1645.400152801825</v>
       </c>
       <c r="F7">
-        <v>116.5531996171184</v>
+        <v>139.863839540542</v>
       </c>
       <c r="G7">
         <v>473.9</v>
@@ -1861,28 +1861,28 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M7">
-        <v>6.445391938826645</v>
+        <v>7.734470326591974</v>
       </c>
       <c r="N7">
-        <v>32.15460806117335</v>
+        <v>30.86552967340802</v>
       </c>
       <c r="O7">
-        <v>6.43092161223467</v>
+        <v>6.173105934681605</v>
       </c>
       <c r="P7">
-        <v>25.72368644893868</v>
+        <v>24.69242373872641</v>
       </c>
       <c r="Q7">
-        <v>211.9236864489387</v>
+        <v>210.8924237387264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09997568552697972</v>
+        <v>0.1004414124603731</v>
       </c>
       <c r="T7">
-        <v>0.8380806251697182</v>
+        <v>0.8452852727103992</v>
       </c>
       <c r="U7">
         <v>0.0553</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.988774672875356</v>
+        <v>4.990645560729464</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09706932771275067</v>
+        <v>0.09708975417487062</v>
       </c>
       <c r="C8">
-        <v>2275.392730502037</v>
+        <v>2251.438178806726</v>
       </c>
       <c r="D8">
-        <v>1941.356570042579</v>
+        <v>1940.712658270692</v>
       </c>
       <c r="E8">
-        <v>-1645.400152801825</v>
+        <v>-1622.089512878401</v>
       </c>
       <c r="F8">
-        <v>139.863839540542</v>
+        <v>163.1744794639657</v>
       </c>
       <c r="G8">
         <v>473.9</v>
@@ -1943,45 +1943,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M8">
-        <v>7.734470326591974</v>
+        <v>9.431484913017217</v>
       </c>
       <c r="N8">
-        <v>30.86552967340802</v>
+        <v>29.16851508698278</v>
       </c>
       <c r="O8">
-        <v>6.173105934681605</v>
+        <v>5.833703017396556</v>
       </c>
       <c r="P8">
-        <v>24.69242373872641</v>
+        <v>23.33481206958622</v>
       </c>
       <c r="Q8">
-        <v>210.8924237387264</v>
+        <v>209.5348120695862</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1004414124603731</v>
+        <v>0.1009171550267426</v>
       </c>
       <c r="T8">
-        <v>0.8452852727103992</v>
+        <v>0.8526448589078691</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.990645560729464</v>
+        <v>4.092674733193366</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09708975417487062</v>
+        <v>0.09739338063699056</v>
       </c>
       <c r="C9">
-        <v>2251.438178806726</v>
+        <v>2218.606313464591</v>
       </c>
       <c r="D9">
-        <v>1940.712658270692</v>
+        <v>1931.19143285198</v>
       </c>
       <c r="E9">
-        <v>-1622.089512878401</v>
+        <v>-1598.778872954978</v>
       </c>
       <c r="F9">
-        <v>163.1744794639657</v>
+        <v>186.4851193873893</v>
       </c>
       <c r="G9">
         <v>473.9</v>
@@ -2025,45 +2025,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M9">
-        <v>9.431484913017218</v>
+        <v>11.95369615273166</v>
       </c>
       <c r="N9">
-        <v>29.16851508698278</v>
+        <v>26.64630384726834</v>
       </c>
       <c r="O9">
-        <v>5.833703017396555</v>
+        <v>5.329260769453668</v>
       </c>
       <c r="P9">
-        <v>23.33481206958622</v>
+        <v>21.31704307781467</v>
       </c>
       <c r="Q9">
-        <v>209.5348120695862</v>
+        <v>207.5170430778147</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1009171550267426</v>
+        <v>0.1014032398228158</v>
       </c>
       <c r="T9">
-        <v>0.8526448589078691</v>
+        <v>0.8601644361096318</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.092674733193365</v>
+        <v>3.229126749317543</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09739338063699056</v>
+        <v>0.0979058070991105</v>
       </c>
       <c r="C10">
-        <v>2218.606313464591</v>
+        <v>2179.436966812744</v>
       </c>
       <c r="D10">
-        <v>1931.19143285198</v>
+        <v>1915.332726123557</v>
       </c>
       <c r="E10">
-        <v>-1598.778872954978</v>
+        <v>-1575.468233031554</v>
       </c>
       <c r="F10">
-        <v>186.4851193873893</v>
+        <v>209.795759310813</v>
       </c>
       <c r="G10">
         <v>473.9</v>
@@ -2107,45 +2107,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M10">
-        <v>11.95369615273166</v>
+        <v>15.08431509444746</v>
       </c>
       <c r="N10">
-        <v>26.64630384726834</v>
+        <v>23.51568490555254</v>
       </c>
       <c r="O10">
-        <v>5.329260769453668</v>
+        <v>4.703136981110508</v>
       </c>
       <c r="P10">
-        <v>21.31704307781467</v>
+        <v>18.81254792444203</v>
       </c>
       <c r="Q10">
-        <v>207.5170430778147</v>
+        <v>205.012547924442</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1014032398228158</v>
+        <v>0.1019000078012203</v>
       </c>
       <c r="T10">
-        <v>0.8601644361096318</v>
+        <v>0.8678492787444001</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.229126749317543</v>
+        <v>2.558949462293364</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0979058070991105</v>
+        <v>0.09823103356123043</v>
       </c>
       <c r="C11">
-        <v>2179.436966812744</v>
+        <v>2146.195546636399</v>
       </c>
       <c r="D11">
-        <v>1915.332726123557</v>
+        <v>1905.401945870635</v>
       </c>
       <c r="E11">
-        <v>-1575.468233031554</v>
+        <v>-1552.15759310813</v>
       </c>
       <c r="F11">
-        <v>209.795759310813</v>
+        <v>233.1063992342367</v>
       </c>
       <c r="G11">
         <v>473.9</v>
@@ -2189,45 +2189,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M11">
-        <v>15.08431509444746</v>
+        <v>17.66946506195514</v>
       </c>
       <c r="N11">
-        <v>23.51568490555254</v>
+        <v>20.93053493804485</v>
       </c>
       <c r="O11">
-        <v>4.703136981110508</v>
+        <v>4.186106987608971</v>
       </c>
       <c r="P11">
-        <v>18.81254792444203</v>
+        <v>16.74442795043588</v>
       </c>
       <c r="Q11">
-        <v>205.012547924442</v>
+        <v>202.9444279504359</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1019000078012203</v>
+        <v>0.1024078150680338</v>
       </c>
       <c r="T11">
-        <v>0.8678492787444001</v>
+        <v>0.8757048956599411</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.558949462293364</v>
+        <v>2.184559626715087</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09823103356123043</v>
+        <v>0.09952506002335036</v>
       </c>
       <c r="C12">
-        <v>2146.195546636399</v>
+        <v>2084.371249845655</v>
       </c>
       <c r="D12">
-        <v>1905.401945870635</v>
+        <v>1866.888289003316</v>
       </c>
       <c r="E12">
-        <v>-1552.15759310813</v>
+        <v>-1528.846953184707</v>
       </c>
       <c r="F12">
-        <v>233.1063992342367</v>
+        <v>256.4170391576604</v>
       </c>
       <c r="G12">
         <v>473.9</v>
@@ -2271,45 +2271,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M12">
-        <v>17.66946506195514</v>
+        <v>23.07753352418943</v>
       </c>
       <c r="N12">
-        <v>20.93053493804485</v>
+        <v>15.52246647581056</v>
       </c>
       <c r="O12">
-        <v>4.18610698760897</v>
+        <v>3.104493295162112</v>
       </c>
       <c r="P12">
-        <v>16.74442795043588</v>
+        <v>12.41797318064845</v>
       </c>
       <c r="Q12">
-        <v>202.9444279504359</v>
+        <v>198.6179731806484</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1024078150680338</v>
+        <v>0.1029270337341015</v>
       </c>
       <c r="T12">
-        <v>0.8757048956599414</v>
+        <v>0.8837370432926854</v>
       </c>
       <c r="U12">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.184559626715087</v>
+        <v>1.672622421262663</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09952506002335036</v>
+        <v>0.09968308648547029</v>
       </c>
       <c r="C13">
-        <v>2084.371249845655</v>
+        <v>2056.463737469672</v>
       </c>
       <c r="D13">
-        <v>1866.888289003316</v>
+        <v>1862.291416550756</v>
       </c>
       <c r="E13">
-        <v>-1528.846953184707</v>
+        <v>-1505.536313261283</v>
       </c>
       <c r="F13">
-        <v>256.4170391576604</v>
+        <v>279.727679081084</v>
       </c>
       <c r="G13">
         <v>473.9</v>
@@ -2353,28 +2353,28 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M13">
-        <v>23.07753352418943</v>
+        <v>25.17549111729756</v>
       </c>
       <c r="N13">
-        <v>15.52246647581056</v>
+        <v>13.42450888270243</v>
       </c>
       <c r="O13">
-        <v>3.104493295162112</v>
+        <v>2.684901776540487</v>
       </c>
       <c r="P13">
-        <v>12.41797318064845</v>
+        <v>10.73960710616195</v>
       </c>
       <c r="Q13">
-        <v>198.6179731806484</v>
+        <v>196.9396071061619</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1029270337341015</v>
+        <v>0.1034580528243981</v>
       </c>
       <c r="T13">
-        <v>0.8837370432926854</v>
+        <v>0.8919517397352649</v>
       </c>
       <c r="U13">
         <v>0.09</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>1.672622421262663</v>
+        <v>1.533237219490774</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09968308648547029</v>
+        <v>0.1064321605652128</v>
       </c>
       <c r="C14">
-        <v>2056.463737469672</v>
+        <v>1855.946359984197</v>
       </c>
       <c r="D14">
-        <v>1862.291416550756</v>
+        <v>1685.084678988705</v>
       </c>
       <c r="E14">
-        <v>-1505.536313261283</v>
+        <v>-1482.225673337859</v>
       </c>
       <c r="F14">
-        <v>279.727679081084</v>
+        <v>303.0383190045077</v>
       </c>
       <c r="G14">
         <v>473.9</v>
@@ -2435,45 +2435,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M14">
-        <v>25.17549111729756</v>
+        <v>44.48602522986173</v>
       </c>
       <c r="N14">
-        <v>13.42450888270243</v>
+        <v>-5.886025229861737</v>
       </c>
       <c r="O14">
-        <v>2.684901776540487</v>
+        <v>-1.177205045972347</v>
       </c>
       <c r="P14">
-        <v>10.73960710616195</v>
+        <v>-4.708820183889389</v>
       </c>
       <c r="Q14">
-        <v>196.9396071061619</v>
+        <v>181.4911798161106</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1034580528243981</v>
+        <v>0.1042068424819688</v>
       </c>
       <c r="T14">
-        <v>0.8919517397352649</v>
+        <v>0.903535277594236</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.2</v>
+        <v>0.1735376437906137</v>
       </c>
       <c r="W14">
-        <v>0.07199999999999999</v>
+        <v>0.1213246738915379</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.533237219490774</v>
+        <v>0.8676882189530685</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1064321605652128</v>
+        <v>0.1074421605652128</v>
       </c>
       <c r="C15">
-        <v>1855.946359984197</v>
+        <v>1808.977026130555</v>
       </c>
       <c r="D15">
-        <v>1685.084678988705</v>
+        <v>1661.425985058487</v>
       </c>
       <c r="E15">
-        <v>-1482.225673337859</v>
+        <v>-1458.915033414436</v>
       </c>
       <c r="F15">
-        <v>303.0383190045077</v>
+        <v>326.3489589279314</v>
       </c>
       <c r="G15">
         <v>473.9</v>
@@ -2517,37 +2517,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M15">
-        <v>44.48602522986173</v>
+        <v>47.90802717062034</v>
       </c>
       <c r="N15">
-        <v>-5.886025229861737</v>
+        <v>-9.308027170620342</v>
       </c>
       <c r="O15">
-        <v>-1.177205045972347</v>
+        <v>-1.861605434124068</v>
       </c>
       <c r="P15">
-        <v>-4.708820183889389</v>
+        <v>-7.446421736496274</v>
       </c>
       <c r="Q15">
-        <v>181.4911798161106</v>
+        <v>178.7535782635037</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1042068424819688</v>
+        <v>0.1048859918131545</v>
       </c>
       <c r="T15">
-        <v>0.903535277594236</v>
+        <v>0.9140415017523085</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.1735376437906137</v>
+        <v>0.1611420978055698</v>
       </c>
       <c r="W15">
-        <v>0.1213246738915379</v>
+        <v>0.1231443400421424</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8676882189530685</v>
+        <v>0.8057104890278491</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1074421605652128</v>
+        <v>0.116867559285127</v>
       </c>
       <c r="C16">
-        <v>1808.977026130555</v>
+        <v>1593.199078128293</v>
       </c>
       <c r="D16">
-        <v>1661.425985058487</v>
+        <v>1468.958676979648</v>
       </c>
       <c r="E16">
-        <v>-1458.915033414436</v>
+        <v>-1435.604393491012</v>
       </c>
       <c r="F16">
-        <v>326.3489589279314</v>
+        <v>349.6595988513551</v>
       </c>
       <c r="G16">
         <v>473.9</v>
@@ -2599,45 +2599,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M16">
-        <v>47.90802717062034</v>
+        <v>70.2116474493521</v>
       </c>
       <c r="N16">
-        <v>-9.308027170620342</v>
+        <v>-31.61164744935211</v>
       </c>
       <c r="O16">
-        <v>-1.861605434124068</v>
+        <v>-6.322329489870421</v>
       </c>
       <c r="P16">
-        <v>-7.446421736496274</v>
+        <v>-25.28931795948169</v>
       </c>
       <c r="Q16">
-        <v>178.7535782635037</v>
+        <v>160.9106820405183</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1048859918131545</v>
+        <v>0.1059521784461495</v>
       </c>
       <c r="T16">
-        <v>0.9140415017523085</v>
+        <v>0.9305350698767599</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.1611420978055698</v>
+        <v>0.1099532667363902</v>
       </c>
       <c r="W16">
-        <v>0.1231443400421424</v>
+        <v>0.1787213840393329</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8057104890278491</v>
+        <v>0.5497663336819507</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.116867559285127</v>
+        <v>0.118417559285127</v>
       </c>
       <c r="C17">
-        <v>1593.199078128293</v>
+        <v>1542.42709449484</v>
       </c>
       <c r="D17">
-        <v>1468.958676979648</v>
+        <v>1441.497333269619</v>
       </c>
       <c r="E17">
-        <v>-1435.604393491012</v>
+        <v>-1412.293753567589</v>
       </c>
       <c r="F17">
-        <v>349.659598851355</v>
+        <v>372.9702387747787</v>
       </c>
       <c r="G17">
         <v>473.9</v>
@@ -2681,37 +2681,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M17">
-        <v>70.2116474493521</v>
+        <v>74.89242394597557</v>
       </c>
       <c r="N17">
-        <v>-31.61164744935211</v>
+        <v>-36.29242394597557</v>
       </c>
       <c r="O17">
-        <v>-6.322329489870421</v>
+        <v>-7.258484789195115</v>
       </c>
       <c r="P17">
-        <v>-25.28931795948169</v>
+        <v>-29.03393915678046</v>
       </c>
       <c r="Q17">
-        <v>160.9106820405183</v>
+        <v>157.1660608432195</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1059521784461495</v>
+        <v>0.1066682758086037</v>
       </c>
       <c r="T17">
-        <v>0.9305350698767599</v>
+        <v>0.9416128683276737</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1099532667363902</v>
+        <v>0.1030811875653658</v>
       </c>
       <c r="W17">
-        <v>0.1787213840393329</v>
+        <v>0.1801012975368746</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5497663336819507</v>
+        <v>0.515405937826829</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.118417559285127</v>
+        <v>0.1260448264782065</v>
       </c>
       <c r="C18">
-        <v>1542.42709449484</v>
+        <v>1397.68144708104</v>
       </c>
       <c r="D18">
-        <v>1441.497333269619</v>
+        <v>1320.062325779243</v>
       </c>
       <c r="E18">
-        <v>-1412.293753567589</v>
+        <v>-1388.983113644165</v>
       </c>
       <c r="F18">
-        <v>372.9702387747787</v>
+        <v>396.2808786982024</v>
       </c>
       <c r="G18">
         <v>473.9</v>
@@ -2763,45 +2763,45 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M18">
-        <v>74.89242394597557</v>
+        <v>93.44303119703613</v>
       </c>
       <c r="N18">
-        <v>-36.29242394597557</v>
+        <v>-54.84303119703614</v>
       </c>
       <c r="O18">
-        <v>-7.258484789195115</v>
+        <v>-10.96860623940723</v>
       </c>
       <c r="P18">
-        <v>-29.03393915678046</v>
+        <v>-43.87442495762891</v>
       </c>
       <c r="Q18">
-        <v>157.1660608432195</v>
+        <v>142.3255750423711</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1066682758086037</v>
+        <v>0.1075549624967549</v>
       </c>
       <c r="T18">
-        <v>0.9416128683276737</v>
+        <v>0.9553296293932141</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.1030811875653658</v>
+        <v>0.08261718290924691</v>
       </c>
       <c r="W18">
-        <v>0.1801012975368746</v>
+        <v>0.2163188682699996</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.515405937826829</v>
+        <v>0.4130859145462346</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1260448264782065</v>
+        <v>0.1279448264782065</v>
       </c>
       <c r="C19">
-        <v>1397.68144708104</v>
+        <v>1347.238316740196</v>
       </c>
       <c r="D19">
-        <v>1320.062325779243</v>
+        <v>1292.929835361822</v>
       </c>
       <c r="E19">
-        <v>-1388.983113644165</v>
+        <v>-1365.672473720741</v>
       </c>
       <c r="F19">
-        <v>396.2808786982024</v>
+        <v>419.5915186216261</v>
       </c>
       <c r="G19">
         <v>473.9</v>
@@ -2845,37 +2845,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M19">
-        <v>93.44303119703613</v>
+        <v>98.93968009097944</v>
       </c>
       <c r="N19">
-        <v>-54.84303119703614</v>
+        <v>-60.33968009097944</v>
       </c>
       <c r="O19">
-        <v>-10.96860623940723</v>
+        <v>-12.06793601819589</v>
       </c>
       <c r="P19">
-        <v>-43.87442495762891</v>
+        <v>-48.27174407278356</v>
       </c>
       <c r="Q19">
-        <v>142.3255750423711</v>
+        <v>137.9282559272164</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1075549624967549</v>
+        <v>0.1083080717954958</v>
       </c>
       <c r="T19">
-        <v>0.9553296293932141</v>
+        <v>0.9669799907272777</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.08261718290924691</v>
+        <v>0.07802733941428874</v>
       </c>
       <c r="W19">
-        <v>0.2163188682699996</v>
+        <v>0.2174011533661107</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.4130859145462346</v>
+        <v>0.3901366970714437</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1279448264782065</v>
+        <v>0.1298448264782065</v>
       </c>
       <c r="C20">
-        <v>1347.238316740197</v>
+        <v>1297.888082582443</v>
       </c>
       <c r="D20">
-        <v>1292.929835361822</v>
+        <v>1266.890241127493</v>
       </c>
       <c r="E20">
-        <v>-1365.672473720741</v>
+        <v>-1342.361833797318</v>
       </c>
       <c r="F20">
-        <v>419.591518621626</v>
+        <v>442.9021585450497</v>
       </c>
       <c r="G20">
         <v>473.9</v>
@@ -2927,37 +2927,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M20">
-        <v>98.93968009097941</v>
+        <v>104.4363289849227</v>
       </c>
       <c r="N20">
-        <v>-60.33968009097941</v>
+        <v>-65.83632898492273</v>
       </c>
       <c r="O20">
-        <v>-12.06793601819588</v>
+        <v>-13.16726579698455</v>
       </c>
       <c r="P20">
-        <v>-48.27174407278353</v>
+        <v>-52.66906318793819</v>
       </c>
       <c r="Q20">
-        <v>137.9282559272165</v>
+        <v>133.5309368120618</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1083080717954958</v>
+        <v>0.1090797763855637</v>
       </c>
       <c r="T20">
-        <v>0.9669799907272777</v>
+        <v>0.9789180153041575</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07802733941428877</v>
+        <v>0.0739206373398525</v>
       </c>
       <c r="W20">
-        <v>0.2174011533661107</v>
+        <v>0.2183695137152628</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3901366970714438</v>
+        <v>0.3696031866992625</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1298448264782065</v>
+        <v>0.1317448264782065</v>
       </c>
       <c r="C21">
-        <v>1297.888082582443</v>
+        <v>1249.566015496153</v>
       </c>
       <c r="D21">
-        <v>1266.890241127493</v>
+        <v>1241.878813964627</v>
       </c>
       <c r="E21">
-        <v>-1342.361833797318</v>
+        <v>-1319.051193873894</v>
       </c>
       <c r="F21">
-        <v>442.9021585450497</v>
+        <v>466.2127984684734</v>
       </c>
       <c r="G21">
         <v>473.9</v>
@@ -3009,37 +3009,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M21">
-        <v>104.4363289849227</v>
+        <v>109.932977878866</v>
       </c>
       <c r="N21">
-        <v>-65.83632898492273</v>
+        <v>-71.33297787886605</v>
       </c>
       <c r="O21">
-        <v>-13.16726579698455</v>
+        <v>-14.26659557577321</v>
       </c>
       <c r="P21">
-        <v>-52.66906318793819</v>
+        <v>-57.06638230309284</v>
       </c>
       <c r="Q21">
-        <v>133.5309368120618</v>
+        <v>129.1336176969072</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1090797763855637</v>
+        <v>0.1098707735903832</v>
       </c>
       <c r="T21">
-        <v>0.9789180153041575</v>
+        <v>0.9911544904954596</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.0739206373398525</v>
+        <v>0.07022460547285987</v>
       </c>
       <c r="W21">
-        <v>0.2183695137152628</v>
+        <v>0.2192410380294997</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3696031866992625</v>
+        <v>0.3511230273642993</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1317448264782065</v>
+        <v>0.1336448264782065</v>
       </c>
       <c r="C22">
-        <v>1249.566015496153</v>
+        <v>1202.212399034362</v>
       </c>
       <c r="D22">
-        <v>1241.878813964627</v>
+        <v>1217.835837426259</v>
       </c>
       <c r="E22">
-        <v>-1319.051193873894</v>
+        <v>-1295.74055395047</v>
       </c>
       <c r="F22">
-        <v>466.2127984684734</v>
+        <v>489.5234383918971</v>
       </c>
       <c r="G22">
         <v>473.9</v>
@@ -3091,37 +3091,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M22">
-        <v>109.932977878866</v>
+        <v>115.4296267728093</v>
       </c>
       <c r="N22">
-        <v>-71.33297787886605</v>
+        <v>-76.82962677280935</v>
       </c>
       <c r="O22">
-        <v>-14.26659557577321</v>
+        <v>-15.36592535456187</v>
       </c>
       <c r="P22">
-        <v>-57.06638230309284</v>
+        <v>-61.46370141824748</v>
       </c>
       <c r="Q22">
-        <v>129.1336176969072</v>
+        <v>124.7362985817525</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1098707735903832</v>
+        <v>0.1106817960408944</v>
       </c>
       <c r="T22">
-        <v>0.9911544904954596</v>
+        <v>1.00370074986882</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.07022460547285987</v>
+        <v>0.06688057664081892</v>
       </c>
       <c r="W22">
-        <v>0.2192410380294997</v>
+        <v>0.2200295600280949</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3511230273642993</v>
+        <v>0.3344028832040946</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1336448264782065</v>
+        <v>0.1355448264782065</v>
       </c>
       <c r="C23">
-        <v>1202.212399034362</v>
+        <v>1155.772053400455</v>
       </c>
       <c r="D23">
-        <v>1217.835837426259</v>
+        <v>1194.706131715776</v>
       </c>
       <c r="E23">
-        <v>-1295.74055395047</v>
+        <v>-1272.429914027046</v>
       </c>
       <c r="F23">
-        <v>489.523438391897</v>
+        <v>512.8340783153208</v>
       </c>
       <c r="G23">
         <v>473.9</v>
@@ -3173,37 +3173,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M23">
-        <v>115.4296267728093</v>
+        <v>120.9262756667526</v>
       </c>
       <c r="N23">
-        <v>-76.82962677280932</v>
+        <v>-82.32627566675265</v>
       </c>
       <c r="O23">
-        <v>-15.36592535456187</v>
+        <v>-16.46525513335053</v>
       </c>
       <c r="P23">
-        <v>-61.46370141824745</v>
+        <v>-65.86102053340213</v>
       </c>
       <c r="Q23">
-        <v>124.7362985817525</v>
+        <v>120.3389794665979</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1106817960408944</v>
+        <v>0.1115136139388546</v>
       </c>
       <c r="T23">
-        <v>1.00370074986882</v>
+        <v>1.016568708200472</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06688057664081894</v>
+        <v>0.06384055042987262</v>
       </c>
       <c r="W23">
-        <v>0.2200295600280949</v>
+        <v>0.2207463982086361</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3344028832040947</v>
+        <v>0.319202752149363</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1355448264782065</v>
+        <v>0.1374448264782065</v>
       </c>
       <c r="C24">
-        <v>1155.772053400455</v>
+        <v>1110.193912666937</v>
       </c>
       <c r="D24">
-        <v>1194.706131715776</v>
+        <v>1172.438630905682</v>
       </c>
       <c r="E24">
-        <v>-1272.429914027046</v>
+        <v>-1249.119274103623</v>
       </c>
       <c r="F24">
-        <v>512.8340783153208</v>
+        <v>536.1447182387444</v>
       </c>
       <c r="G24">
         <v>473.9</v>
@@ -3255,37 +3255,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M24">
-        <v>120.9262756667526</v>
+        <v>126.4229245606959</v>
       </c>
       <c r="N24">
-        <v>-82.32627566675265</v>
+        <v>-87.82292456069594</v>
       </c>
       <c r="O24">
-        <v>-16.46525513335053</v>
+        <v>-17.56458491213919</v>
       </c>
       <c r="P24">
-        <v>-65.86102053340213</v>
+        <v>-70.25833964855676</v>
       </c>
       <c r="Q24">
-        <v>120.3389794665979</v>
+        <v>115.9416603514432</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1115136139388546</v>
+        <v>0.112367037496502</v>
       </c>
       <c r="T24">
-        <v>1.016568708200472</v>
+        <v>1.029770899216062</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06384055042987262</v>
+        <v>0.06106487432422598</v>
       </c>
       <c r="W24">
-        <v>0.2207463982086361</v>
+        <v>0.2214009026343475</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.319202752149363</v>
+        <v>0.3053243716211299</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1374448264782065</v>
+        <v>0.1393448264782065</v>
       </c>
       <c r="C25">
-        <v>1110.193912666937</v>
+        <v>1065.430648409089</v>
       </c>
       <c r="D25">
-        <v>1172.438630905682</v>
+        <v>1150.986006571257</v>
       </c>
       <c r="E25">
-        <v>-1249.119274103623</v>
+        <v>-1225.808634180199</v>
       </c>
       <c r="F25">
-        <v>536.1447182387444</v>
+        <v>559.4553581621681</v>
       </c>
       <c r="G25">
         <v>473.9</v>
@@ -3337,37 +3337,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M25">
-        <v>126.4229245606959</v>
+        <v>131.9195734546392</v>
       </c>
       <c r="N25">
-        <v>-87.82292456069594</v>
+        <v>-93.31957345463925</v>
       </c>
       <c r="O25">
-        <v>-17.56458491213919</v>
+        <v>-18.66391469092785</v>
       </c>
       <c r="P25">
-        <v>-70.25833964855676</v>
+        <v>-74.6556587637114</v>
       </c>
       <c r="Q25">
-        <v>115.9416603514432</v>
+        <v>111.5443412362886</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.112367037496502</v>
+        <v>0.1132429195688244</v>
       </c>
       <c r="T25">
-        <v>1.029770899216062</v>
+        <v>1.04332051631101</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.06106487432422598</v>
+        <v>0.05852050456071656</v>
       </c>
       <c r="W25">
-        <v>0.2214009026343475</v>
+        <v>0.222000865024583</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3053243716211299</v>
+        <v>0.2926025228035828</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1393448264782065</v>
+        <v>0.1412448264782065</v>
       </c>
       <c r="C26">
-        <v>1065.430648409089</v>
+        <v>1021.438333915407</v>
       </c>
       <c r="D26">
-        <v>1150.986006571257</v>
+        <v>1130.304332000999</v>
       </c>
       <c r="E26">
-        <v>-1225.808634180199</v>
+        <v>-1202.497994256775</v>
       </c>
       <c r="F26">
-        <v>559.4553581621681</v>
+        <v>582.7659980855917</v>
       </c>
       <c r="G26">
         <v>473.9</v>
@@ -3419,37 +3419,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M26">
-        <v>131.9195734546392</v>
+        <v>137.4162223485825</v>
       </c>
       <c r="N26">
-        <v>-93.31957345463925</v>
+        <v>-98.81622234858253</v>
       </c>
       <c r="O26">
-        <v>-18.66391469092785</v>
+        <v>-19.76324446971651</v>
       </c>
       <c r="P26">
-        <v>-74.6556587637114</v>
+        <v>-79.05297787886602</v>
       </c>
       <c r="Q26">
-        <v>111.5443412362886</v>
+        <v>107.147022121134</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1132429195688244</v>
+        <v>0.1141421584964088</v>
       </c>
       <c r="T26">
-        <v>1.04332051631101</v>
+        <v>1.05723145652849</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05852050456071656</v>
+        <v>0.05617968437828791</v>
       </c>
       <c r="W26">
-        <v>0.222000865024583</v>
+        <v>0.2225528304235997</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2926025228035828</v>
+        <v>0.2808984218914395</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1412448264782065</v>
+        <v>0.1431448264782065</v>
       </c>
       <c r="C27">
-        <v>1021.438333915407</v>
+        <v>978.1761439611569</v>
       </c>
       <c r="D27">
-        <v>1130.304332000999</v>
+        <v>1110.352781970172</v>
       </c>
       <c r="E27">
-        <v>-1202.497994256775</v>
+        <v>-1179.187354333352</v>
       </c>
       <c r="F27">
-        <v>582.7659980855917</v>
+        <v>606.0766380090154</v>
       </c>
       <c r="G27">
         <v>473.9</v>
@@ -3501,37 +3501,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M27">
-        <v>137.4162223485825</v>
+        <v>142.9128712425258</v>
       </c>
       <c r="N27">
-        <v>-98.81622234858253</v>
+        <v>-104.3128712425258</v>
       </c>
       <c r="O27">
-        <v>-19.76324446971651</v>
+        <v>-20.86257424850517</v>
       </c>
       <c r="P27">
-        <v>-79.05297787886602</v>
+        <v>-83.45029699402066</v>
       </c>
       <c r="Q27">
-        <v>107.147022121134</v>
+        <v>102.7497030059793</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1141421584964088</v>
+        <v>0.1150657011787927</v>
       </c>
       <c r="T27">
-        <v>1.05723145652849</v>
+        <v>1.071518368103199</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05617968437828791</v>
+        <v>0.05401892728681529</v>
       </c>
       <c r="W27">
-        <v>0.2225528304235997</v>
+        <v>0.223062336945769</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2808984218914395</v>
+        <v>0.2700946364340765</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1431448264782065</v>
+        <v>0.1450448264782065</v>
       </c>
       <c r="C28">
-        <v>978.1761439611569</v>
+        <v>935.6060858270527</v>
       </c>
       <c r="D28">
-        <v>1110.352781970172</v>
+        <v>1091.093363759492</v>
       </c>
       <c r="E28">
-        <v>-1179.187354333352</v>
+        <v>-1155.876714409928</v>
       </c>
       <c r="F28">
-        <v>606.0766380090154</v>
+        <v>629.3872779324391</v>
       </c>
       <c r="G28">
         <v>473.9</v>
@@ -3583,37 +3583,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M28">
-        <v>142.9128712425258</v>
+        <v>148.4095201364692</v>
       </c>
       <c r="N28">
-        <v>-104.3128712425258</v>
+        <v>-109.8095201364692</v>
       </c>
       <c r="O28">
-        <v>-20.86257424850517</v>
+        <v>-21.96190402729383</v>
       </c>
       <c r="P28">
-        <v>-83.45029699402066</v>
+        <v>-87.84761610917533</v>
       </c>
       <c r="Q28">
-        <v>102.7497030059793</v>
+        <v>98.35238389082465</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1150657011787927</v>
+        <v>0.11601454640042</v>
       </c>
       <c r="T28">
-        <v>1.071518368103199</v>
+        <v>1.086196701912832</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05401892728681529</v>
+        <v>0.05201822627619249</v>
       </c>
       <c r="W28">
-        <v>0.223062336945769</v>
+        <v>0.2235341022440738</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2700946364340765</v>
+        <v>0.2600911313809625</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1450448264782065</v>
+        <v>0.1469448264782065</v>
       </c>
       <c r="C29">
-        <v>935.6060858270527</v>
+        <v>893.6927578340623</v>
       </c>
       <c r="D29">
-        <v>1091.093363759492</v>
+        <v>1072.490675689925</v>
       </c>
       <c r="E29">
-        <v>-1155.876714409928</v>
+        <v>-1132.566074486504</v>
       </c>
       <c r="F29">
-        <v>629.3872779324391</v>
+        <v>652.6979178558628</v>
       </c>
       <c r="G29">
         <v>473.9</v>
@@ -3665,37 +3665,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M29">
-        <v>148.4095201364692</v>
+        <v>153.9061690304125</v>
       </c>
       <c r="N29">
-        <v>-109.8095201364692</v>
+        <v>-115.3061690304125</v>
       </c>
       <c r="O29">
-        <v>-21.96190402729383</v>
+        <v>-23.06123380608249</v>
       </c>
       <c r="P29">
-        <v>-87.84761610917533</v>
+        <v>-92.24493522432996</v>
       </c>
       <c r="Q29">
-        <v>98.35238389082465</v>
+        <v>93.95506477567002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.11601454640042</v>
+        <v>0.1169897484337591</v>
       </c>
       <c r="T29">
-        <v>1.086196701912832</v>
+        <v>1.101282767217177</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05201822627619249</v>
+        <v>0.05016043248061419</v>
       </c>
       <c r="W29">
-        <v>0.2235341022440738</v>
+        <v>0.2239721700210712</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2600911313809625</v>
+        <v>0.250802162403071</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1469448264782065</v>
+        <v>0.1488448264782065</v>
       </c>
       <c r="C30">
-        <v>893.6927578340623</v>
+        <v>852.403132165403</v>
       </c>
       <c r="D30">
-        <v>1072.490675689925</v>
+        <v>1054.511689944689</v>
       </c>
       <c r="E30">
-        <v>-1132.566074486504</v>
+        <v>-1109.255434563081</v>
       </c>
       <c r="F30">
-        <v>652.6979178558628</v>
+        <v>676.0085577792864</v>
       </c>
       <c r="G30">
         <v>473.9</v>
@@ -3747,37 +3747,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M30">
-        <v>153.9061690304125</v>
+        <v>159.4028179243558</v>
       </c>
       <c r="N30">
-        <v>-115.3061690304125</v>
+        <v>-120.8028179243558</v>
       </c>
       <c r="O30">
-        <v>-23.06123380608249</v>
+        <v>-24.16056358487116</v>
       </c>
       <c r="P30">
-        <v>-92.24493522432996</v>
+        <v>-96.64225433948461</v>
       </c>
       <c r="Q30">
-        <v>93.95506477567002</v>
+        <v>89.55774566051538</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1169897484337591</v>
+        <v>0.1179924209469107</v>
       </c>
       <c r="T30">
-        <v>1.101282767217177</v>
+        <v>1.11679379210756</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.05016043248061419</v>
+        <v>0.04843076239507577</v>
       </c>
       <c r="W30">
-        <v>0.2239721700210712</v>
+        <v>0.2243800262272411</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.250802162403071</v>
+        <v>0.2421538119753789</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1488448264782065</v>
+        <v>0.1507448264782065</v>
       </c>
       <c r="C31">
-        <v>852.4031321654031</v>
+        <v>811.7063591727223</v>
       </c>
       <c r="D31">
-        <v>1054.51168994469</v>
+        <v>1037.125556875432</v>
       </c>
       <c r="E31">
-        <v>-1109.255434563081</v>
+        <v>-1085.944794639657</v>
       </c>
       <c r="F31">
-        <v>676.0085577792863</v>
+        <v>699.3191977027101</v>
       </c>
       <c r="G31">
         <v>473.9</v>
@@ -3829,37 +3829,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M31">
-        <v>159.4028179243557</v>
+        <v>164.899466818299</v>
       </c>
       <c r="N31">
-        <v>-120.8028179243557</v>
+        <v>-126.299466818299</v>
       </c>
       <c r="O31">
-        <v>-24.16056358487115</v>
+        <v>-25.25989336365981</v>
       </c>
       <c r="P31">
-        <v>-96.64225433948459</v>
+        <v>-101.0395734546392</v>
       </c>
       <c r="Q31">
-        <v>89.55774566051539</v>
+        <v>85.16042654536076</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1179924209469107</v>
+        <v>0.1190237412461522</v>
       </c>
       <c r="T31">
-        <v>1.11679379210756</v>
+        <v>1.132747989137668</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04843076239507578</v>
+        <v>0.04681640364857326</v>
       </c>
       <c r="W31">
-        <v>0.2243800262272411</v>
+        <v>0.2247606920196664</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2421538119753789</v>
+        <v>0.2340820182428662</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1507448264782065</v>
+        <v>0.1526448264782065</v>
       </c>
       <c r="C32">
-        <v>811.7063591727223</v>
+        <v>771.5735907271388</v>
       </c>
       <c r="D32">
-        <v>1037.125556875432</v>
+        <v>1020.303428353272</v>
       </c>
       <c r="E32">
-        <v>-1085.944794639657</v>
+        <v>-1062.634154716233</v>
       </c>
       <c r="F32">
-        <v>699.3191977027101</v>
+        <v>722.6298376261337</v>
       </c>
       <c r="G32">
         <v>473.9</v>
@@ -3911,37 +3911,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M32">
-        <v>164.899466818299</v>
+        <v>170.3961157122423</v>
       </c>
       <c r="N32">
-        <v>-126.299466818299</v>
+        <v>-131.7961157122423</v>
       </c>
       <c r="O32">
-        <v>-25.25989336365981</v>
+        <v>-26.35922314244847</v>
       </c>
       <c r="P32">
-        <v>-101.0395734546392</v>
+        <v>-105.4368925697939</v>
       </c>
       <c r="Q32">
-        <v>85.16042654536076</v>
+        <v>80.76310743020612</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1190237412461522</v>
+        <v>0.1200849548874008</v>
       </c>
       <c r="T32">
-        <v>1.132747989137668</v>
+        <v>1.149164626661402</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04681640364857326</v>
+        <v>0.04530619707926444</v>
       </c>
       <c r="W32">
-        <v>0.2247606920196664</v>
+        <v>0.2251167987287095</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2340820182428662</v>
+        <v>0.2265309853963222</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1526448264782065</v>
+        <v>0.1545448264782065</v>
       </c>
       <c r="C33">
-        <v>771.5735907271388</v>
+        <v>731.9778204873231</v>
       </c>
       <c r="D33">
-        <v>1020.303428353272</v>
+        <v>1004.018298036881</v>
       </c>
       <c r="E33">
-        <v>-1062.634154716233</v>
+        <v>-1039.32351479281</v>
       </c>
       <c r="F33">
-        <v>722.6298376261337</v>
+        <v>745.9404775495574</v>
       </c>
       <c r="G33">
         <v>473.9</v>
@@ -3993,37 +3993,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M33">
-        <v>170.3961157122423</v>
+        <v>175.8927646061856</v>
       </c>
       <c r="N33">
-        <v>-131.7961157122423</v>
+        <v>-137.2927646061856</v>
       </c>
       <c r="O33">
-        <v>-26.35922314244847</v>
+        <v>-27.45855292123713</v>
       </c>
       <c r="P33">
-        <v>-105.4368925697939</v>
+        <v>-109.8342116849485</v>
       </c>
       <c r="Q33">
-        <v>80.76310743020612</v>
+        <v>76.36578831505147</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1200849548874008</v>
+        <v>0.1211773806945685</v>
       </c>
       <c r="T33">
-        <v>1.149164626661402</v>
+        <v>1.166064106465246</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04530619707926444</v>
+        <v>0.04389037842053743</v>
       </c>
       <c r="W33">
-        <v>0.2251167987287095</v>
+        <v>0.2254506487684373</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2265309853963222</v>
+        <v>0.2194518921026871</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1545448264782065</v>
+        <v>0.1564448264782065</v>
       </c>
       <c r="C34">
-        <v>731.9778204873231</v>
+        <v>692.8937392242069</v>
       </c>
       <c r="D34">
-        <v>1004.018298036881</v>
+        <v>988.2448566971881</v>
       </c>
       <c r="E34">
-        <v>-1039.32351479281</v>
+        <v>-1016.012874869386</v>
       </c>
       <c r="F34">
-        <v>745.9404775495574</v>
+        <v>769.2511174729812</v>
       </c>
       <c r="G34">
         <v>473.9</v>
@@ -4075,37 +4075,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M34">
-        <v>175.8927646061856</v>
+        <v>181.389413500129</v>
       </c>
       <c r="N34">
-        <v>-137.2927646061856</v>
+        <v>-142.789413500129</v>
       </c>
       <c r="O34">
-        <v>-27.45855292123713</v>
+        <v>-28.5578827000258</v>
       </c>
       <c r="P34">
-        <v>-109.8342116849485</v>
+        <v>-114.2315308001032</v>
       </c>
       <c r="Q34">
-        <v>76.36578831505147</v>
+        <v>71.96846919989682</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1211773806945685</v>
+        <v>0.1223024162273233</v>
       </c>
       <c r="T34">
-        <v>1.166064106465246</v>
+        <v>1.183468048352788</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04389037842053743</v>
+        <v>0.04256036695324841</v>
       </c>
       <c r="W34">
-        <v>0.2254506487684373</v>
+        <v>0.225764265472424</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2194518921026871</v>
+        <v>0.212801834766242</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1564448264782065</v>
+        <v>0.1583448264782065</v>
       </c>
       <c r="C35">
-        <v>692.8937392242069</v>
+        <v>654.2976035721206</v>
       </c>
       <c r="D35">
-        <v>988.2448566971881</v>
+        <v>972.9593609685254</v>
       </c>
       <c r="E35">
-        <v>-1016.012874869386</v>
+        <v>-992.7022349459623</v>
       </c>
       <c r="F35">
-        <v>769.2511174729812</v>
+        <v>792.5617573964048</v>
       </c>
       <c r="G35">
         <v>473.9</v>
@@ -4157,37 +4157,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M35">
-        <v>181.389413500129</v>
+        <v>186.8860623940723</v>
       </c>
       <c r="N35">
-        <v>-142.789413500129</v>
+        <v>-148.2860623940723</v>
       </c>
       <c r="O35">
-        <v>-28.5578827000258</v>
+        <v>-29.65721247881446</v>
       </c>
       <c r="P35">
-        <v>-114.2315308001032</v>
+        <v>-118.6288499152578</v>
       </c>
       <c r="Q35">
-        <v>71.96846919989682</v>
+        <v>67.57115008474217</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1223024162273233</v>
+        <v>0.1234615437459191</v>
       </c>
       <c r="T35">
-        <v>1.183468048352788</v>
+        <v>1.201399382418739</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04256036695324841</v>
+        <v>0.04130859145462346</v>
       </c>
       <c r="W35">
-        <v>0.225764265472424</v>
+        <v>0.2260594341349998</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.212801834766242</v>
+        <v>0.2065429572731172</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1583448264782065</v>
+        <v>0.1602448264782065</v>
       </c>
       <c r="C36">
-        <v>654.2976035721206</v>
+        <v>616.1671167748127</v>
       </c>
       <c r="D36">
-        <v>972.9593609685254</v>
+        <v>958.1395140946412</v>
       </c>
       <c r="E36">
-        <v>-992.7022349459623</v>
+        <v>-969.3915950225387</v>
       </c>
       <c r="F36">
-        <v>792.5617573964048</v>
+        <v>815.8723973198285</v>
       </c>
       <c r="G36">
         <v>473.9</v>
@@ -4239,37 +4239,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M36">
-        <v>186.8860623940723</v>
+        <v>192.3827112880155</v>
       </c>
       <c r="N36">
-        <v>-148.2860623940723</v>
+        <v>-153.7827112880155</v>
       </c>
       <c r="O36">
-        <v>-29.65721247881446</v>
+        <v>-30.75654225760311</v>
       </c>
       <c r="P36">
-        <v>-118.6288499152578</v>
+        <v>-123.0261690304124</v>
       </c>
       <c r="Q36">
-        <v>67.57115008474217</v>
+        <v>63.17383096958756</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1234615437459191</v>
+        <v>0.1246563367266255</v>
       </c>
       <c r="T36">
-        <v>1.201399382418739</v>
+        <v>1.219882449840566</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04130859145462346</v>
+        <v>0.04012834598449136</v>
       </c>
       <c r="W36">
-        <v>0.2260594341349998</v>
+        <v>0.2263377360168569</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2065429572731172</v>
+        <v>0.2006417299224568</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1602448264782065</v>
+        <v>0.1621448264782065</v>
       </c>
       <c r="C37">
-        <v>616.1671167748127</v>
+        <v>578.4813201666105</v>
       </c>
       <c r="D37">
-        <v>958.1395140946412</v>
+        <v>943.7643574098628</v>
       </c>
       <c r="E37">
-        <v>-969.3915950225387</v>
+        <v>-946.0809550991149</v>
       </c>
       <c r="F37">
-        <v>815.8723973198285</v>
+        <v>839.1830372432522</v>
       </c>
       <c r="G37">
         <v>473.9</v>
@@ -4321,37 +4321,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M37">
-        <v>192.3827112880155</v>
+        <v>197.8793601819589</v>
       </c>
       <c r="N37">
-        <v>-153.7827112880155</v>
+        <v>-159.2793601819589</v>
       </c>
       <c r="O37">
-        <v>-30.75654225760311</v>
+        <v>-31.85587203639178</v>
       </c>
       <c r="P37">
-        <v>-123.0261690304124</v>
+        <v>-127.4234881455671</v>
       </c>
       <c r="Q37">
-        <v>63.17383096958756</v>
+        <v>58.77651185443288</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1246563367266255</v>
+        <v>0.125888466987979</v>
       </c>
       <c r="T37">
-        <v>1.219882449840566</v>
+        <v>1.238943113119325</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04012834598449136</v>
+        <v>0.03901366970714437</v>
       </c>
       <c r="W37">
-        <v>0.2263377360168569</v>
+        <v>0.2266005766830554</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2006417299224568</v>
+        <v>0.1950683485357219</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1621448264782065</v>
+        <v>0.1640448264782065</v>
       </c>
       <c r="C38">
-        <v>578.4813201666108</v>
+        <v>541.2204942779688</v>
       </c>
       <c r="D38">
-        <v>943.7643574098628</v>
+        <v>929.8141714446446</v>
       </c>
       <c r="E38">
-        <v>-946.0809550991152</v>
+        <v>-922.7703151756914</v>
       </c>
       <c r="F38">
-        <v>839.183037243252</v>
+        <v>862.4936771666758</v>
       </c>
       <c r="G38">
         <v>473.9</v>
@@ -4403,37 +4403,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M38">
-        <v>197.8793601819588</v>
+        <v>203.3760090759021</v>
       </c>
       <c r="N38">
-        <v>-159.2793601819588</v>
+        <v>-164.7760090759022</v>
       </c>
       <c r="O38">
-        <v>-31.85587203639177</v>
+        <v>-32.95520181518043</v>
       </c>
       <c r="P38">
-        <v>-127.4234881455671</v>
+        <v>-131.8208072607217</v>
       </c>
       <c r="Q38">
-        <v>58.77651185443293</v>
+        <v>54.37919273927827</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.125888466987979</v>
+        <v>0.1271597124957247</v>
       </c>
       <c r="T38">
-        <v>1.238943113119324</v>
+        <v>1.258608876819631</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03901366970714439</v>
+        <v>0.03795924620154589</v>
       </c>
       <c r="W38">
-        <v>0.2266005766830554</v>
+        <v>0.2268492097456755</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1950683485357219</v>
+        <v>0.1897962310077294</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1640448264782065</v>
+        <v>0.1659448264782065</v>
       </c>
       <c r="C39">
-        <v>541.2204942779688</v>
+        <v>504.3660685840621</v>
       </c>
       <c r="D39">
-        <v>929.8141714446446</v>
+        <v>916.2703856741614</v>
       </c>
       <c r="E39">
-        <v>-922.7703151756914</v>
+        <v>-899.4596752522677</v>
       </c>
       <c r="F39">
-        <v>862.4936771666758</v>
+        <v>885.8043170900994</v>
       </c>
       <c r="G39">
         <v>473.9</v>
@@ -4485,37 +4485,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M39">
-        <v>203.3760090759021</v>
+        <v>208.8726579698454</v>
       </c>
       <c r="N39">
-        <v>-164.7760090759022</v>
+        <v>-170.2726579698455</v>
       </c>
       <c r="O39">
-        <v>-32.95520181518043</v>
+        <v>-34.0545315939691</v>
       </c>
       <c r="P39">
-        <v>-131.8208072607217</v>
+        <v>-136.2181263758764</v>
       </c>
       <c r="Q39">
-        <v>54.37919273927827</v>
+        <v>49.98187362412364</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1271597124957247</v>
+        <v>0.1284719659230751</v>
       </c>
       <c r="T39">
-        <v>1.258608876819631</v>
+        <v>1.278909019994141</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03795924620154589</v>
+        <v>0.03696031866992625</v>
       </c>
       <c r="W39">
-        <v>0.2268492097456755</v>
+        <v>0.2270847568576314</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1897962310077294</v>
+        <v>0.1848015933496312</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1659448264782065</v>
+        <v>0.1678448264782065</v>
       </c>
       <c r="C40">
-        <v>504.3660685840621</v>
+        <v>467.9005390278172</v>
       </c>
       <c r="D40">
-        <v>916.2703856741614</v>
+        <v>903.1154960413404</v>
       </c>
       <c r="E40">
-        <v>-899.4596752522677</v>
+        <v>-876.149035328844</v>
       </c>
       <c r="F40">
-        <v>885.8043170900994</v>
+        <v>909.1149570135232</v>
       </c>
       <c r="G40">
         <v>473.9</v>
@@ -4567,37 +4567,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M40">
-        <v>208.8726579698454</v>
+        <v>214.3693068637888</v>
       </c>
       <c r="N40">
-        <v>-170.2726579698455</v>
+        <v>-175.7693068637888</v>
       </c>
       <c r="O40">
-        <v>-34.0545315939691</v>
+        <v>-35.15386137275776</v>
       </c>
       <c r="P40">
-        <v>-136.2181263758764</v>
+        <v>-140.615445491031</v>
       </c>
       <c r="Q40">
-        <v>49.98187362412364</v>
+        <v>45.58455450896895</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1284719659230751</v>
+        <v>0.1298272440529616</v>
       </c>
       <c r="T40">
-        <v>1.278909019994141</v>
+        <v>1.29987474163339</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03696031866992625</v>
+        <v>0.03601261819121019</v>
       </c>
       <c r="W40">
-        <v>0.2270847568576314</v>
+        <v>0.2273082246305126</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1848015933496312</v>
+        <v>0.1800630909560509</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1678448264782065</v>
+        <v>0.1697448264782065</v>
       </c>
       <c r="C41">
-        <v>467.9005390278172</v>
+        <v>431.8073925471123</v>
       </c>
       <c r="D41">
-        <v>903.1154960413404</v>
+        <v>890.3329894840591</v>
       </c>
       <c r="E41">
-        <v>-876.149035328844</v>
+        <v>-852.8383954054203</v>
       </c>
       <c r="F41">
-        <v>909.1149570135232</v>
+        <v>932.4255969369468</v>
       </c>
       <c r="G41">
         <v>473.9</v>
@@ -4649,37 +4649,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M41">
-        <v>214.3693068637888</v>
+        <v>219.8659557577321</v>
       </c>
       <c r="N41">
-        <v>-175.7693068637888</v>
+        <v>-181.2659557577321</v>
       </c>
       <c r="O41">
-        <v>-35.15386137275776</v>
+        <v>-36.25319115154642</v>
       </c>
       <c r="P41">
-        <v>-140.615445491031</v>
+        <v>-145.0127646061857</v>
       </c>
       <c r="Q41">
-        <v>45.58455450896895</v>
+        <v>41.18723539381432</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1298272440529616</v>
+        <v>0.131227698120511</v>
       </c>
       <c r="T41">
-        <v>1.29987474163339</v>
+        <v>1.321539320660613</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03601261819121019</v>
+        <v>0.03511230273642994</v>
       </c>
       <c r="W41">
-        <v>0.2273082246305126</v>
+        <v>0.2275205190147498</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1800630909560509</v>
+        <v>0.1755615136821497</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1697448264782065</v>
+        <v>0.1716448264782065</v>
       </c>
       <c r="C42">
-        <v>431.8073925471123</v>
+        <v>396.0710379218834</v>
       </c>
       <c r="D42">
-        <v>890.3329894840591</v>
+        <v>877.9072747822538</v>
       </c>
       <c r="E42">
-        <v>-852.8383954054203</v>
+        <v>-829.5277554819967</v>
       </c>
       <c r="F42">
-        <v>932.4255969369468</v>
+        <v>955.7362368603705</v>
       </c>
       <c r="G42">
         <v>473.9</v>
@@ -4731,37 +4731,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M42">
-        <v>219.8659557577321</v>
+        <v>225.3626046516754</v>
       </c>
       <c r="N42">
-        <v>-181.2659557577321</v>
+        <v>-186.7626046516754</v>
       </c>
       <c r="O42">
-        <v>-36.25319115154642</v>
+        <v>-37.35252093033507</v>
       </c>
       <c r="P42">
-        <v>-145.0127646061857</v>
+        <v>-149.4100837213403</v>
       </c>
       <c r="Q42">
-        <v>41.18723539381432</v>
+        <v>36.78991627865969</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.131227698120511</v>
+        <v>0.1326756252072993</v>
       </c>
       <c r="T42">
-        <v>1.321539320660613</v>
+        <v>1.343938292197233</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03511230273642994</v>
+        <v>0.03425590510871214</v>
       </c>
       <c r="W42">
-        <v>0.2275205190147498</v>
+        <v>0.2277224575753657</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1755615136821497</v>
+        <v>0.1712795255435606</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1716448264782065</v>
+        <v>0.1735448264782065</v>
       </c>
       <c r="C43">
-        <v>396.0710379218834</v>
+        <v>360.6767423322185</v>
       </c>
       <c r="D43">
-        <v>877.9072747822538</v>
+        <v>865.8236191160129</v>
       </c>
       <c r="E43">
-        <v>-829.5277554819967</v>
+        <v>-806.2171155585729</v>
       </c>
       <c r="F43">
-        <v>955.7362368603705</v>
+        <v>979.0468767837942</v>
       </c>
       <c r="G43">
         <v>473.9</v>
@@ -4813,37 +4813,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M43">
-        <v>225.3626046516754</v>
+        <v>230.8592535456187</v>
       </c>
       <c r="N43">
-        <v>-186.7626046516754</v>
+        <v>-192.2592535456187</v>
       </c>
       <c r="O43">
-        <v>-37.35252093033507</v>
+        <v>-38.45185070912374</v>
       </c>
       <c r="P43">
-        <v>-149.4100837213403</v>
+        <v>-153.807402836495</v>
       </c>
       <c r="Q43">
-        <v>36.78991627865969</v>
+        <v>32.39259716350503</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1326756252072993</v>
+        <v>0.1341734808143217</v>
       </c>
       <c r="T43">
-        <v>1.343938292197233</v>
+        <v>1.367109642062703</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03425590510871214</v>
+        <v>0.03344028832040946</v>
       </c>
       <c r="W43">
-        <v>0.2277224575753657</v>
+        <v>0.2279147800140475</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1712795255435606</v>
+        <v>0.1672014416020473</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1735448264782065</v>
+        <v>0.1754448264782065</v>
       </c>
       <c r="C44">
-        <v>360.6767423322187</v>
+        <v>325.610573084666</v>
       </c>
       <c r="D44">
-        <v>865.8236191160129</v>
+        <v>854.0680897918837</v>
       </c>
       <c r="E44">
-        <v>-806.2171155585731</v>
+        <v>-782.9064756351494</v>
       </c>
       <c r="F44">
-        <v>979.046876783794</v>
+        <v>1002.357516707218</v>
       </c>
       <c r="G44">
         <v>473.9</v>
@@ -4895,37 +4895,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M44">
-        <v>230.8592535456186</v>
+        <v>236.355902439562</v>
       </c>
       <c r="N44">
-        <v>-192.2592535456186</v>
+        <v>-197.755902439562</v>
       </c>
       <c r="O44">
-        <v>-38.45185070912373</v>
+        <v>-39.5511804879124</v>
       </c>
       <c r="P44">
-        <v>-153.8074028364949</v>
+        <v>-158.2047219516496</v>
       </c>
       <c r="Q44">
-        <v>32.39259716350509</v>
+        <v>27.99527804835043</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1341734808143217</v>
+        <v>0.1357238927584326</v>
       </c>
       <c r="T44">
-        <v>1.367109642062703</v>
+        <v>1.391094021748013</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03344028832040947</v>
+        <v>0.03266260719667901</v>
       </c>
       <c r="W44">
-        <v>0.2279147800140475</v>
+        <v>0.2280981572230231</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1672014416020473</v>
+        <v>0.1633130359833951</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1754448264782065</v>
+        <v>0.1773448264782065</v>
       </c>
       <c r="C45">
-        <v>325.610573084666</v>
+        <v>290.8593440221348</v>
       </c>
       <c r="D45">
-        <v>854.0680897918837</v>
+        <v>842.6275006527765</v>
       </c>
       <c r="E45">
-        <v>-782.9064756351494</v>
+        <v>-759.5958357117256</v>
       </c>
       <c r="F45">
-        <v>1002.357516707218</v>
+        <v>1025.668156630642</v>
       </c>
       <c r="G45">
         <v>473.9</v>
@@ -4977,37 +4977,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M45">
-        <v>236.355902439562</v>
+        <v>241.8525513335053</v>
       </c>
       <c r="N45">
-        <v>-197.755902439562</v>
+        <v>-203.2525513335053</v>
       </c>
       <c r="O45">
-        <v>-39.5511804879124</v>
+        <v>-40.65051026670106</v>
       </c>
       <c r="P45">
-        <v>-158.2047219516496</v>
+        <v>-162.6020410668042</v>
       </c>
       <c r="Q45">
-        <v>27.99527804835043</v>
+        <v>23.59795893319574</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1357238927584326</v>
+        <v>0.1373296765576903</v>
       </c>
       <c r="T45">
-        <v>1.391094021748013</v>
+        <v>1.415934986422085</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03266260719667901</v>
+        <v>0.03192027521493631</v>
       </c>
       <c r="W45">
-        <v>0.2280981572230231</v>
+        <v>0.228273199104318</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1633130359833951</v>
+        <v>0.1596013760746815</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1773448264782065</v>
+        <v>0.1792448264782065</v>
       </c>
       <c r="C46">
-        <v>290.8593440221348</v>
+        <v>256.4105661840363</v>
       </c>
       <c r="D46">
-        <v>842.6275006527765</v>
+        <v>831.4893627381015</v>
       </c>
       <c r="E46">
-        <v>-759.5958357117256</v>
+        <v>-736.285195788302</v>
       </c>
       <c r="F46">
-        <v>1025.668156630642</v>
+        <v>1048.978796554065</v>
       </c>
       <c r="G46">
         <v>473.9</v>
@@ -5059,37 +5059,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M46">
-        <v>241.8525513335053</v>
+        <v>247.3492002274486</v>
       </c>
       <c r="N46">
-        <v>-203.2525513335053</v>
+        <v>-208.7492002274486</v>
       </c>
       <c r="O46">
-        <v>-40.65051026670106</v>
+        <v>-41.74984004548972</v>
       </c>
       <c r="P46">
-        <v>-162.6020410668042</v>
+        <v>-166.9993601819589</v>
       </c>
       <c r="Q46">
-        <v>23.59795893319574</v>
+        <v>19.20063981804111</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1373296765576903</v>
+        <v>0.1389938524951028</v>
       </c>
       <c r="T46">
-        <v>1.415934986422085</v>
+        <v>1.441679258902486</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03192027521493631</v>
+        <v>0.0312109357657155</v>
       </c>
       <c r="W46">
-        <v>0.228273199104318</v>
+        <v>0.2284404613464443</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1596013760746815</v>
+        <v>0.1560546788285775</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1792448264782065</v>
+        <v>0.1811448264782065</v>
       </c>
       <c r="C47">
-        <v>256.4105661840363</v>
+        <v>222.2524023285162</v>
       </c>
       <c r="D47">
-        <v>831.4893627381015</v>
+        <v>820.641838806005</v>
       </c>
       <c r="E47">
-        <v>-736.285195788302</v>
+        <v>-712.9745558648783</v>
       </c>
       <c r="F47">
-        <v>1048.978796554065</v>
+        <v>1072.289436477489</v>
       </c>
       <c r="G47">
         <v>473.9</v>
@@ -5141,37 +5141,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M47">
-        <v>247.3492002274486</v>
+        <v>252.8458491213919</v>
       </c>
       <c r="N47">
-        <v>-208.7492002274486</v>
+        <v>-214.2458491213919</v>
       </c>
       <c r="O47">
-        <v>-41.74984004548972</v>
+        <v>-42.84916982427838</v>
       </c>
       <c r="P47">
-        <v>-166.9993601819589</v>
+        <v>-171.3966792971135</v>
       </c>
       <c r="Q47">
-        <v>19.20063981804111</v>
+        <v>14.80332070288648</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1389938524951028</v>
+        <v>0.1407196645783455</v>
       </c>
       <c r="T47">
-        <v>1.441679258902486</v>
+        <v>1.468377022956237</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0312109357657155</v>
+        <v>0.03053243716211299</v>
       </c>
       <c r="W47">
-        <v>0.2284404613464443</v>
+        <v>0.2286004513171738</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1560546788285775</v>
+        <v>0.1526621858105649</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1811448264782065</v>
+        <v>0.1830448264782065</v>
       </c>
       <c r="C48">
-        <v>222.2524023285162</v>
+        <v>188.3736249686356</v>
       </c>
       <c r="D48">
-        <v>820.641838806005</v>
+        <v>810.0737013695482</v>
       </c>
       <c r="E48">
-        <v>-712.9745558648783</v>
+        <v>-689.6639159414547</v>
       </c>
       <c r="F48">
-        <v>1072.289436477489</v>
+        <v>1095.600076400912</v>
       </c>
       <c r="G48">
         <v>473.9</v>
@@ -5223,37 +5223,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M48">
-        <v>252.8458491213919</v>
+        <v>258.3424980153352</v>
       </c>
       <c r="N48">
-        <v>-214.2458491213919</v>
+        <v>-219.7424980153352</v>
       </c>
       <c r="O48">
-        <v>-42.84916982427838</v>
+        <v>-43.94849960306704</v>
       </c>
       <c r="P48">
-        <v>-171.3966792971135</v>
+        <v>-175.7939984122682</v>
       </c>
       <c r="Q48">
-        <v>14.80332070288648</v>
+        <v>10.40600158773182</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1407196645783455</v>
+        <v>0.1425106016458615</v>
       </c>
       <c r="T48">
-        <v>1.468377022956237</v>
+        <v>1.496082249804467</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03053243716211299</v>
+        <v>0.02988281083951484</v>
       </c>
       <c r="W48">
-        <v>0.2286004513171738</v>
+        <v>0.2287536332040424</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1526621858105649</v>
+        <v>0.1494140541975741</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1830448264782065</v>
+        <v>0.1849448264782065</v>
       </c>
       <c r="C49">
-        <v>188.3736249686356</v>
+        <v>154.7635776097609</v>
       </c>
       <c r="D49">
-        <v>810.0737013695482</v>
+        <v>799.7742939340972</v>
       </c>
       <c r="E49">
-        <v>-689.6639159414547</v>
+        <v>-666.353276018031</v>
       </c>
       <c r="F49">
-        <v>1095.600076400912</v>
+        <v>1118.910716324336</v>
       </c>
       <c r="G49">
         <v>473.9</v>
@@ -5305,37 +5305,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M49">
-        <v>258.3424980153352</v>
+        <v>263.8391469092785</v>
       </c>
       <c r="N49">
-        <v>-219.7424980153352</v>
+        <v>-225.2391469092785</v>
       </c>
       <c r="O49">
-        <v>-43.94849960306704</v>
+        <v>-45.04782938185571</v>
       </c>
       <c r="P49">
-        <v>-175.7939984122682</v>
+        <v>-180.1913175274228</v>
       </c>
       <c r="Q49">
-        <v>10.40600158773182</v>
+        <v>6.008682472577192</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1425106016458615</v>
+        <v>0.1443704209082819</v>
       </c>
       <c r="T49">
-        <v>1.496082249804467</v>
+        <v>1.524853062300707</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02988281083951484</v>
+        <v>0.02926025228035828</v>
       </c>
       <c r="W49">
-        <v>0.2287536332040424</v>
+        <v>0.2289004325122915</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1494140541975741</v>
+        <v>0.1463012614017913</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1849448264782065</v>
+        <v>0.1868448264782065</v>
       </c>
       <c r="C50">
-        <v>154.7635776097613</v>
+        <v>121.412138906833</v>
       </c>
       <c r="D50">
-        <v>799.7742939340974</v>
+        <v>789.7334951545928</v>
       </c>
       <c r="E50">
-        <v>-666.353276018031</v>
+        <v>-643.0426360946074</v>
       </c>
       <c r="F50">
-        <v>1118.910716324336</v>
+        <v>1142.22135624776</v>
       </c>
       <c r="G50">
         <v>473.9</v>
@@ -5387,37 +5387,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M50">
-        <v>263.8391469092785</v>
+        <v>269.3357958032217</v>
       </c>
       <c r="N50">
-        <v>-225.2391469092785</v>
+        <v>-230.7357958032217</v>
       </c>
       <c r="O50">
-        <v>-45.04782938185571</v>
+        <v>-46.14715916064435</v>
       </c>
       <c r="P50">
-        <v>-180.1913175274228</v>
+        <v>-184.5886366425774</v>
       </c>
       <c r="Q50">
-        <v>6.008682472577192</v>
+        <v>1.61136335742259</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1443704209082819</v>
+        <v>0.1463031742594246</v>
       </c>
       <c r="T50">
-        <v>1.524853062300707</v>
+        <v>1.554752141953662</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02926025228035828</v>
+        <v>0.02866310427463669</v>
       </c>
       <c r="W50">
-        <v>0.2289004325122915</v>
+        <v>0.2290412400120407</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1463012614017913</v>
+        <v>0.1433155213731835</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1868448264782065</v>
+        <v>0.1887448264782065</v>
       </c>
       <c r="C51">
-        <v>121.412138906833</v>
+        <v>88.30968948809505</v>
       </c>
       <c r="D51">
-        <v>789.7334951545928</v>
+        <v>779.9416856592784</v>
       </c>
       <c r="E51">
-        <v>-643.0426360946074</v>
+        <v>-619.7319961711837</v>
       </c>
       <c r="F51">
-        <v>1142.22135624776</v>
+        <v>1165.531996171183</v>
       </c>
       <c r="G51">
         <v>473.9</v>
@@ -5469,37 +5469,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M51">
-        <v>269.3357958032217</v>
+        <v>274.832444697165</v>
       </c>
       <c r="N51">
-        <v>-230.7357958032217</v>
+        <v>-236.2324446971651</v>
       </c>
       <c r="O51">
-        <v>-46.14715916064435</v>
+        <v>-47.24648893943301</v>
       </c>
       <c r="P51">
-        <v>-184.5886366425774</v>
+        <v>-188.985955757732</v>
       </c>
       <c r="Q51">
-        <v>1.61136335742259</v>
+        <v>-2.78595575773204</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1463031742594246</v>
+        <v>0.1483132377446131</v>
       </c>
       <c r="T51">
-        <v>1.554752141953662</v>
+        <v>1.585847184792735</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02866310427463669</v>
+        <v>0.02808984218914395</v>
       </c>
       <c r="W51">
-        <v>0.2290412400120407</v>
+        <v>0.2291764152117998</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1433155213731835</v>
+        <v>0.1404492109457197</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1887448264782065</v>
+        <v>0.1906448264782065</v>
       </c>
       <c r="C52">
-        <v>88.30968948809505</v>
+        <v>55.44708121668486</v>
       </c>
       <c r="D52">
-        <v>779.9416856592784</v>
+        <v>770.3897173112921</v>
       </c>
       <c r="E52">
-        <v>-619.7319961711837</v>
+        <v>-596.4213562477601</v>
       </c>
       <c r="F52">
-        <v>1165.531996171183</v>
+        <v>1188.842636094607</v>
       </c>
       <c r="G52">
         <v>473.9</v>
@@ -5551,37 +5551,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M52">
-        <v>274.832444697165</v>
+        <v>280.3290935911083</v>
       </c>
       <c r="N52">
-        <v>-236.2324446971651</v>
+        <v>-241.7290935911084</v>
       </c>
       <c r="O52">
-        <v>-47.24648893943301</v>
+        <v>-48.34581871822167</v>
       </c>
       <c r="P52">
-        <v>-188.985955757732</v>
+        <v>-193.3832748728867</v>
       </c>
       <c r="Q52">
-        <v>-2.78595575773204</v>
+        <v>-7.183274872886699</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1483132377446131</v>
+        <v>0.1504053446373604</v>
       </c>
       <c r="T52">
-        <v>1.585847184792735</v>
+        <v>1.618211413053811</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02808984218914395</v>
+        <v>0.02753906096974898</v>
       </c>
       <c r="W52">
-        <v>0.2291764152117998</v>
+        <v>0.2293062894233332</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1404492109457197</v>
+        <v>0.1376953048487448</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1906448264782065</v>
+        <v>0.1925448264782065</v>
       </c>
       <c r="C53">
-        <v>55.44708121668486</v>
+        <v>22.81560868362521</v>
       </c>
       <c r="D53">
-        <v>770.3897173112921</v>
+        <v>761.068884701656</v>
       </c>
       <c r="E53">
-        <v>-596.4213562477601</v>
+        <v>-573.1107163243364</v>
       </c>
       <c r="F53">
-        <v>1188.842636094607</v>
+        <v>1212.153276018031</v>
       </c>
       <c r="G53">
         <v>473.9</v>
@@ -5633,37 +5633,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M53">
-        <v>280.3290935911083</v>
+        <v>285.8257424850516</v>
       </c>
       <c r="N53">
-        <v>-241.7290935911084</v>
+        <v>-247.2257424850517</v>
       </c>
       <c r="O53">
-        <v>-48.34581871822167</v>
+        <v>-49.44514849701034</v>
       </c>
       <c r="P53">
-        <v>-193.3832748728867</v>
+        <v>-197.7805939880413</v>
       </c>
       <c r="Q53">
-        <v>-7.183274872886699</v>
+        <v>-11.58059398804133</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1504053446373604</v>
+        <v>0.1525846226506387</v>
       </c>
       <c r="T53">
-        <v>1.618211413053811</v>
+        <v>1.651924150825766</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02753906096974898</v>
+        <v>0.02700946364340764</v>
       </c>
       <c r="W53">
-        <v>0.2293062894233332</v>
+        <v>0.2294311684728845</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1376953048487448</v>
+        <v>0.1350473182170382</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1925448264782065</v>
+        <v>0.1944448264782065</v>
       </c>
       <c r="C54">
-        <v>22.81560868362521</v>
+        <v>-9.593017254514052</v>
       </c>
       <c r="D54">
-        <v>761.068884701656</v>
+        <v>751.9708986869407</v>
       </c>
       <c r="E54">
-        <v>-573.1107163243364</v>
+        <v>-549.8000764009125</v>
       </c>
       <c r="F54">
-        <v>1212.153276018031</v>
+        <v>1235.463915941455</v>
       </c>
       <c r="G54">
         <v>473.9</v>
@@ -5715,37 +5715,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M54">
-        <v>285.8257424850516</v>
+        <v>291.322391378995</v>
       </c>
       <c r="N54">
-        <v>-247.2257424850517</v>
+        <v>-252.722391378995</v>
       </c>
       <c r="O54">
-        <v>-49.44514849701034</v>
+        <v>-50.54447827579901</v>
       </c>
       <c r="P54">
-        <v>-197.7805939880413</v>
+        <v>-202.177913103196</v>
       </c>
       <c r="Q54">
-        <v>-11.58059398804133</v>
+        <v>-15.97791310319602</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1525846226506387</v>
+        <v>0.1548566358985246</v>
       </c>
       <c r="T54">
-        <v>1.651924150825766</v>
+        <v>1.687071473183761</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02700946364340764</v>
+        <v>0.02649985112183391</v>
       </c>
       <c r="W54">
-        <v>0.2294311684728845</v>
+        <v>0.2295513351054716</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1350473182170382</v>
+        <v>0.1324992556091695</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1944448264782065</v>
+        <v>0.1963448264782065</v>
       </c>
       <c r="C55">
-        <v>-9.593017254514052</v>
+        <v>-41.78669406235053</v>
       </c>
       <c r="D55">
-        <v>751.9708986869407</v>
+        <v>743.0878618025278</v>
       </c>
       <c r="E55">
-        <v>-549.8000764009125</v>
+        <v>-526.4894364774889</v>
       </c>
       <c r="F55">
-        <v>1235.463915941455</v>
+        <v>1258.774555864878</v>
       </c>
       <c r="G55">
         <v>473.9</v>
@@ -5797,37 +5797,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M55">
-        <v>291.322391378995</v>
+        <v>296.8190402729383</v>
       </c>
       <c r="N55">
-        <v>-252.722391378995</v>
+        <v>-258.2190402729383</v>
       </c>
       <c r="O55">
-        <v>-50.54447827579901</v>
+        <v>-51.64380805458766</v>
       </c>
       <c r="P55">
-        <v>-202.177913103196</v>
+        <v>-206.5752322183506</v>
       </c>
       <c r="Q55">
-        <v>-15.97791310319602</v>
+        <v>-20.37523221835065</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1548566358985246</v>
+        <v>0.1572274323311013</v>
       </c>
       <c r="T55">
-        <v>1.687071473183761</v>
+        <v>1.723746939992104</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02649985112183391</v>
+        <v>0.02600911313809625</v>
       </c>
       <c r="W55">
-        <v>0.2295513351054716</v>
+        <v>0.2296670511220369</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1324992556091695</v>
+        <v>0.1300455656904813</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1963448264782065</v>
+        <v>0.1982448264782065</v>
       </c>
       <c r="C56">
-        <v>-41.78669406235053</v>
+        <v>-73.7729503901171</v>
       </c>
       <c r="D56">
-        <v>743.0878618025278</v>
+        <v>734.4122453981848</v>
       </c>
       <c r="E56">
-        <v>-526.4894364774889</v>
+        <v>-503.1787965540652</v>
       </c>
       <c r="F56">
-        <v>1258.774555864878</v>
+        <v>1282.085195788302</v>
       </c>
       <c r="G56">
         <v>473.9</v>
@@ -5879,37 +5879,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M56">
-        <v>296.8190402729383</v>
+        <v>302.3156891668816</v>
       </c>
       <c r="N56">
-        <v>-258.2190402729383</v>
+        <v>-263.7156891668816</v>
       </c>
       <c r="O56">
-        <v>-51.64380805458766</v>
+        <v>-52.74313783337632</v>
       </c>
       <c r="P56">
-        <v>-206.5752322183506</v>
+        <v>-210.9725513335053</v>
       </c>
       <c r="Q56">
-        <v>-20.37523221835065</v>
+        <v>-24.77255133350528</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1572274323311013</v>
+        <v>0.1597035974940146</v>
       </c>
       <c r="T56">
-        <v>1.723746939992104</v>
+        <v>1.762052427547484</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02600911313809625</v>
+        <v>0.02553622017194904</v>
       </c>
       <c r="W56">
-        <v>0.2296670511220369</v>
+        <v>0.2297785592834544</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1300455656904813</v>
+        <v>0.1276811008597453</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1982448264782065</v>
+        <v>0.2001448264782065</v>
       </c>
       <c r="C57">
-        <v>-73.7729503901171</v>
+        <v>-105.5589673548998</v>
       </c>
       <c r="D57">
-        <v>734.4122453981848</v>
+        <v>725.9368683568258</v>
       </c>
       <c r="E57">
-        <v>-503.1787965540652</v>
+        <v>-479.8681566306416</v>
       </c>
       <c r="F57">
-        <v>1282.085195788302</v>
+        <v>1305.395835711726</v>
       </c>
       <c r="G57">
         <v>473.9</v>
@@ -5961,37 +5961,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M57">
-        <v>302.3156891668816</v>
+        <v>307.8123380608249</v>
       </c>
       <c r="N57">
-        <v>-263.7156891668816</v>
+        <v>-269.2123380608249</v>
       </c>
       <c r="O57">
-        <v>-52.74313783337632</v>
+        <v>-53.84246761216498</v>
       </c>
       <c r="P57">
-        <v>-210.9725513335053</v>
+        <v>-215.3698704486599</v>
       </c>
       <c r="Q57">
-        <v>-24.77255133350528</v>
+        <v>-29.16987044865994</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1597035974940146</v>
+        <v>0.1622923156188786</v>
       </c>
       <c r="T57">
-        <v>1.762052427547484</v>
+        <v>1.802099073628109</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02553622017194904</v>
+        <v>0.0250802162403071</v>
       </c>
       <c r="W57">
-        <v>0.2297785592834544</v>
+        <v>0.2298860850105356</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1276811008597453</v>
+        <v>0.1254010812015356</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2001448264782065</v>
+        <v>0.2020448264782065</v>
       </c>
       <c r="C58">
-        <v>-105.5589673548998</v>
+        <v>-137.1515983651357</v>
       </c>
       <c r="D58">
-        <v>725.9368683568258</v>
+        <v>717.6548772700137</v>
       </c>
       <c r="E58">
-        <v>-479.8681566306416</v>
+        <v>-456.5575167072179</v>
       </c>
       <c r="F58">
-        <v>1305.395835711726</v>
+        <v>1328.706475635149</v>
       </c>
       <c r="G58">
         <v>473.9</v>
@@ -6043,37 +6043,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M58">
-        <v>307.8123380608249</v>
+        <v>313.3089869547682</v>
       </c>
       <c r="N58">
-        <v>-269.2123380608249</v>
+        <v>-274.7089869547682</v>
       </c>
       <c r="O58">
-        <v>-53.84246761216498</v>
+        <v>-54.94179739095364</v>
       </c>
       <c r="P58">
-        <v>-215.3698704486599</v>
+        <v>-219.7671895638146</v>
       </c>
       <c r="Q58">
-        <v>-29.16987044865994</v>
+        <v>-33.56718956381457</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1622923156188786</v>
+        <v>0.1650014392379223</v>
       </c>
       <c r="T58">
-        <v>1.802099073628109</v>
+        <v>1.844008354410158</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0250802162403071</v>
+        <v>0.0246402124466175</v>
       </c>
       <c r="W58">
-        <v>0.2298860850105356</v>
+        <v>0.2299898379050876</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1254010812015356</v>
+        <v>0.1232010622330876</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2020448264782065</v>
+        <v>0.2039448264782065</v>
       </c>
       <c r="C59">
-        <v>-137.1515983651357</v>
+        <v>-168.5573876033855</v>
       </c>
       <c r="D59">
-        <v>717.6548772700137</v>
+        <v>709.5597279551874</v>
       </c>
       <c r="E59">
-        <v>-456.5575167072179</v>
+        <v>-433.2468767837943</v>
       </c>
       <c r="F59">
-        <v>1328.706475635149</v>
+        <v>1352.017115558573</v>
       </c>
       <c r="G59">
         <v>473.9</v>
@@ -6125,37 +6125,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M59">
-        <v>313.3089869547682</v>
+        <v>318.8056358487115</v>
       </c>
       <c r="N59">
-        <v>-274.7089869547682</v>
+        <v>-280.2056358487115</v>
       </c>
       <c r="O59">
-        <v>-54.94179739095364</v>
+        <v>-56.0411271697423</v>
       </c>
       <c r="P59">
-        <v>-219.7671895638146</v>
+        <v>-224.1645086789692</v>
       </c>
       <c r="Q59">
-        <v>-33.56718956381457</v>
+        <v>-37.9645086789692</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1650014392379223</v>
+        <v>0.1678395687435871</v>
       </c>
       <c r="T59">
-        <v>1.844008354410158</v>
+        <v>1.887913315229447</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0246402124466175</v>
+        <v>0.02421538119753789</v>
       </c>
       <c r="W59">
-        <v>0.2299898379050876</v>
+        <v>0.2300900131136206</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1232010622330876</v>
+        <v>0.1210769059876895</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2039448264782065</v>
+        <v>0.2058448264782065</v>
       </c>
       <c r="C60">
-        <v>-168.5573876033852</v>
+        <v>-199.7825872721444</v>
       </c>
       <c r="D60">
-        <v>709.5597279551874</v>
+        <v>701.6451682098518</v>
       </c>
       <c r="E60">
-        <v>-433.2468767837945</v>
+        <v>-409.9362368603709</v>
       </c>
       <c r="F60">
-        <v>1352.017115558573</v>
+        <v>1375.327755481996</v>
       </c>
       <c r="G60">
         <v>473.9</v>
@@ -6207,37 +6207,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M60">
-        <v>318.8056358487115</v>
+        <v>324.3022847426548</v>
       </c>
       <c r="N60">
-        <v>-280.2056358487115</v>
+        <v>-285.7022847426548</v>
       </c>
       <c r="O60">
-        <v>-56.0411271697423</v>
+        <v>-57.14045694853096</v>
       </c>
       <c r="P60">
-        <v>-224.1645086789692</v>
+        <v>-228.5618277941238</v>
       </c>
       <c r="Q60">
-        <v>-37.9645086789692</v>
+        <v>-42.36182779412385</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1678395687435871</v>
+        <v>0.1708161435909916</v>
       </c>
       <c r="T60">
-        <v>1.887913315229447</v>
+        <v>1.933959981454555</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02421538119753789</v>
+        <v>0.02380495100774911</v>
       </c>
       <c r="W60">
-        <v>0.2300900131136206</v>
+        <v>0.2301867925523728</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1210769059876894</v>
+        <v>0.1190247550387454</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2058448264782065</v>
+        <v>0.2077448264782065</v>
       </c>
       <c r="C61">
-        <v>-199.7825872721444</v>
+        <v>-230.83317369821</v>
       </c>
       <c r="D61">
-        <v>701.6451682098518</v>
+        <v>693.9052217072102</v>
       </c>
       <c r="E61">
-        <v>-409.9362368603709</v>
+        <v>-386.625596936947</v>
       </c>
       <c r="F61">
-        <v>1375.327755481996</v>
+        <v>1398.63839540542</v>
       </c>
       <c r="G61">
         <v>473.9</v>
@@ -6289,37 +6289,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M61">
-        <v>324.3022847426548</v>
+        <v>329.7989336365981</v>
       </c>
       <c r="N61">
-        <v>-285.7022847426548</v>
+        <v>-291.1989336365981</v>
       </c>
       <c r="O61">
-        <v>-57.14045694853096</v>
+        <v>-58.23978672731963</v>
       </c>
       <c r="P61">
-        <v>-228.5618277941238</v>
+        <v>-232.9591469092785</v>
       </c>
       <c r="Q61">
-        <v>-42.36182779412385</v>
+        <v>-46.75914690927848</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1708161435909916</v>
+        <v>0.1739415471807664</v>
       </c>
       <c r="T61">
-        <v>1.933959981454555</v>
+        <v>1.982308980990919</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02380495100774911</v>
+        <v>0.02340820182428663</v>
       </c>
       <c r="W61">
-        <v>0.2301867925523728</v>
+        <v>0.2302803460098332</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1190247550387454</v>
+        <v>0.117041009121433</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2077448264782065</v>
+        <v>0.2096448264782065</v>
       </c>
       <c r="C62">
-        <v>-230.83317369821</v>
+        <v>-261.714862382777</v>
       </c>
       <c r="D62">
-        <v>693.9052217072102</v>
+        <v>686.3341729460668</v>
       </c>
       <c r="E62">
-        <v>-386.625596936947</v>
+        <v>-363.3149570135233</v>
       </c>
       <c r="F62">
-        <v>1398.63839540542</v>
+        <v>1421.949035328844</v>
       </c>
       <c r="G62">
         <v>473.9</v>
@@ -6371,37 +6371,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M62">
-        <v>329.7989336365981</v>
+        <v>335.2955825305414</v>
       </c>
       <c r="N62">
-        <v>-291.1989336365981</v>
+        <v>-296.6955825305414</v>
       </c>
       <c r="O62">
-        <v>-58.23978672731963</v>
+        <v>-59.33911650610828</v>
       </c>
       <c r="P62">
-        <v>-232.9591469092785</v>
+        <v>-237.3564660244331</v>
       </c>
       <c r="Q62">
-        <v>-46.75914690927848</v>
+        <v>-51.15646602443314</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1739415471807664</v>
+        <v>0.1772272278777092</v>
       </c>
       <c r="T62">
-        <v>1.982308980990919</v>
+        <v>2.033137416400943</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02340820182428663</v>
+        <v>0.02302446081077373</v>
       </c>
       <c r="W62">
-        <v>0.2302803460098332</v>
+        <v>0.2303708321408196</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.117041009121433</v>
+        <v>0.1151223040538686</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2096448264782065</v>
+        <v>0.2115448264782065</v>
       </c>
       <c r="C63">
-        <v>-261.714862382777</v>
+        <v>-292.4331220769225</v>
       </c>
       <c r="D63">
-        <v>686.3341729460668</v>
+        <v>678.926553175345</v>
       </c>
       <c r="E63">
-        <v>-363.3149570135233</v>
+        <v>-340.0043170900997</v>
       </c>
       <c r="F63">
-        <v>1421.949035328844</v>
+        <v>1445.259675252267</v>
       </c>
       <c r="G63">
         <v>473.9</v>
@@ -6453,37 +6453,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M63">
-        <v>335.2955825305414</v>
+        <v>340.7922314244847</v>
       </c>
       <c r="N63">
-        <v>-296.6955825305414</v>
+        <v>-302.1922314244847</v>
       </c>
       <c r="O63">
-        <v>-59.33911650610828</v>
+        <v>-60.43844628489694</v>
       </c>
       <c r="P63">
-        <v>-237.3564660244331</v>
+        <v>-241.7537851395878</v>
       </c>
       <c r="Q63">
-        <v>-51.15646602443314</v>
+        <v>-55.55378513958777</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1772272278777092</v>
+        <v>0.1806858391376489</v>
       </c>
       <c r="T63">
-        <v>2.033137416400943</v>
+        <v>2.08664103262202</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02302446081077373</v>
+        <v>0.02265309853963222</v>
       </c>
       <c r="W63">
-        <v>0.2303708321408196</v>
+        <v>0.2304583993643547</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1151223040538686</v>
+        <v>0.113265492698161</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2115448264782065</v>
+        <v>0.2134448264782065</v>
       </c>
       <c r="C64">
-        <v>-292.4331220769225</v>
+        <v>-322.993187955318</v>
       </c>
       <c r="D64">
-        <v>678.926553175345</v>
+        <v>671.6771272203731</v>
       </c>
       <c r="E64">
-        <v>-340.0043170900997</v>
+        <v>-316.693677166676</v>
       </c>
       <c r="F64">
-        <v>1445.259675252267</v>
+        <v>1468.570315175691</v>
       </c>
       <c r="G64">
         <v>473.9</v>
@@ -6535,37 +6535,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M64">
-        <v>340.7922314244847</v>
+        <v>346.288880318428</v>
       </c>
       <c r="N64">
-        <v>-302.1922314244847</v>
+        <v>-307.688880318428</v>
       </c>
       <c r="O64">
-        <v>-60.43844628489694</v>
+        <v>-61.53777606368561</v>
       </c>
       <c r="P64">
-        <v>-241.7537851395878</v>
+        <v>-246.1511042547424</v>
       </c>
       <c r="Q64">
-        <v>-55.55378513958777</v>
+        <v>-59.9511042547424</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1806858391376489</v>
+        <v>0.1843314023575853</v>
       </c>
       <c r="T64">
-        <v>2.08664103262202</v>
+        <v>2.143036736206399</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02265309853963222</v>
+        <v>0.02229352554693964</v>
       </c>
       <c r="W64">
-        <v>0.2304583993643547</v>
+        <v>0.2305431866760316</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.113265492698161</v>
+        <v>0.1114676277346981</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2134448264782065</v>
+        <v>0.2153448264782065</v>
       </c>
       <c r="C65">
-        <v>-322.993187955318</v>
+        <v>-353.400073954863</v>
       </c>
       <c r="D65">
-        <v>671.6771272203731</v>
+        <v>664.5808811442516</v>
       </c>
       <c r="E65">
-        <v>-316.693677166676</v>
+        <v>-293.3830372432524</v>
       </c>
       <c r="F65">
-        <v>1468.570315175691</v>
+        <v>1491.880955099115</v>
       </c>
       <c r="G65">
         <v>473.9</v>
@@ -6617,37 +6617,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M65">
-        <v>346.288880318428</v>
+        <v>351.7855292123713</v>
       </c>
       <c r="N65">
-        <v>-307.688880318428</v>
+        <v>-313.1855292123713</v>
       </c>
       <c r="O65">
-        <v>-61.53777606368561</v>
+        <v>-62.63710584247426</v>
       </c>
       <c r="P65">
-        <v>-246.1511042547424</v>
+        <v>-250.5484233698971</v>
       </c>
       <c r="Q65">
-        <v>-59.9511042547424</v>
+        <v>-64.34842336989706</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1843314023575853</v>
+        <v>0.1881794968675183</v>
       </c>
       <c r="T65">
-        <v>2.143036736206399</v>
+        <v>2.202565534434354</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02229352554693964</v>
+        <v>0.02194518921026871</v>
       </c>
       <c r="W65">
-        <v>0.2305431866760316</v>
+        <v>0.2306253243842186</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1114676277346981</v>
+        <v>0.1097259460513434</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2153448264782065</v>
+        <v>0.2172448264782065</v>
       </c>
       <c r="C66">
-        <v>-353.400073954863</v>
+        <v>-383.6585843393532</v>
       </c>
       <c r="D66">
-        <v>664.5808811442516</v>
+        <v>657.6330106831853</v>
       </c>
       <c r="E66">
-        <v>-293.3830372432524</v>
+        <v>-270.0723973198287</v>
       </c>
       <c r="F66">
-        <v>1491.880955099115</v>
+        <v>1515.191595022538</v>
       </c>
       <c r="G66">
         <v>473.9</v>
@@ -6699,37 +6699,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M66">
-        <v>351.7855292123713</v>
+        <v>357.2821781063146</v>
       </c>
       <c r="N66">
-        <v>-313.1855292123713</v>
+        <v>-318.6821781063146</v>
       </c>
       <c r="O66">
-        <v>-62.63710584247426</v>
+        <v>-63.73643562126293</v>
       </c>
       <c r="P66">
-        <v>-250.5484233698971</v>
+        <v>-254.9457424850517</v>
       </c>
       <c r="Q66">
-        <v>-64.34842336989706</v>
+        <v>-68.74574248505169</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1881794968675183</v>
+        <v>0.1922474824923045</v>
       </c>
       <c r="T66">
-        <v>2.202565534434354</v>
+        <v>2.265495978275336</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02194518921026871</v>
+        <v>0.02160757091472612</v>
       </c>
       <c r="W66">
-        <v>0.2306253243842186</v>
+        <v>0.2307049347783076</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1097259460513434</v>
+        <v>0.1080378545736305</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2172448264782065</v>
+        <v>0.2191448264782065</v>
       </c>
       <c r="C67">
-        <v>-383.6585843393532</v>
+        <v>-413.773324546235</v>
       </c>
       <c r="D67">
-        <v>657.6330106831853</v>
+        <v>650.8289103997273</v>
       </c>
       <c r="E67">
-        <v>-270.0723973198287</v>
+        <v>-246.7617573964048</v>
       </c>
       <c r="F67">
-        <v>1515.191595022538</v>
+        <v>1538.502234945962</v>
       </c>
       <c r="G67">
         <v>473.9</v>
@@ -6781,37 +6781,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M67">
-        <v>357.2821781063146</v>
+        <v>362.7788270002579</v>
       </c>
       <c r="N67">
-        <v>-318.6821781063146</v>
+        <v>-324.1788270002579</v>
       </c>
       <c r="O67">
-        <v>-63.73643562126293</v>
+        <v>-64.83576540005159</v>
       </c>
       <c r="P67">
-        <v>-254.9457424850517</v>
+        <v>-259.3430616002063</v>
       </c>
       <c r="Q67">
-        <v>-68.74574248505169</v>
+        <v>-73.14306160020635</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1922474824923045</v>
+        <v>0.196554761389137</v>
       </c>
       <c r="T67">
-        <v>2.265495978275336</v>
+        <v>2.332128212930493</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02160757091472612</v>
+        <v>0.0212801834766242</v>
       </c>
       <c r="W67">
-        <v>0.2307049347783076</v>
+        <v>0.230782132736212</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1080378545736305</v>
+        <v>0.1064009173831211</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2191448264782065</v>
+        <v>0.2210448264782065</v>
       </c>
       <c r="C68">
-        <v>-413.773324546235</v>
+        <v>-443.7487113669099</v>
       </c>
       <c r="D68">
-        <v>650.8289103997273</v>
+        <v>644.1641635024761</v>
       </c>
       <c r="E68">
-        <v>-246.7617573964048</v>
+        <v>-223.4511174729812</v>
       </c>
       <c r="F68">
-        <v>1538.502234945962</v>
+        <v>1561.812874869386</v>
       </c>
       <c r="G68">
         <v>473.9</v>
@@ -6863,37 +6863,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M68">
-        <v>362.7788270002579</v>
+        <v>368.2754758942012</v>
       </c>
       <c r="N68">
-        <v>-324.1788270002579</v>
+        <v>-329.6754758942012</v>
       </c>
       <c r="O68">
-        <v>-64.83576540005159</v>
+        <v>-65.93509517884024</v>
       </c>
       <c r="P68">
-        <v>-259.3430616002063</v>
+        <v>-263.740380715361</v>
       </c>
       <c r="Q68">
-        <v>-73.14306160020635</v>
+        <v>-77.54038071536098</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.196554761389137</v>
+        <v>0.2011230874918381</v>
       </c>
       <c r="T68">
-        <v>2.332128212930493</v>
+        <v>2.402798764837478</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0212801834766242</v>
+        <v>0.02096256879786862</v>
       </c>
       <c r="W68">
-        <v>0.230782132736212</v>
+        <v>0.2308570262774626</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1064009173831211</v>
+        <v>0.1048128439893432</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2210448264782065</v>
+        <v>0.2229448264782065</v>
       </c>
       <c r="C69">
-        <v>-443.7487113669099</v>
+        <v>-473.5889825078775</v>
       </c>
       <c r="D69">
-        <v>644.1641635024761</v>
+        <v>637.6345322849322</v>
       </c>
       <c r="E69">
-        <v>-223.4511174729812</v>
+        <v>-200.1404775495575</v>
       </c>
       <c r="F69">
-        <v>1561.812874869386</v>
+        <v>1585.12351479281</v>
       </c>
       <c r="G69">
         <v>473.9</v>
@@ -6945,37 +6945,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M69">
-        <v>368.2754758942012</v>
+        <v>373.7721247881445</v>
       </c>
       <c r="N69">
-        <v>-329.6754758942012</v>
+        <v>-335.1721247881445</v>
       </c>
       <c r="O69">
-        <v>-65.93509517884024</v>
+        <v>-67.0344249576289</v>
       </c>
       <c r="P69">
-        <v>-263.740380715361</v>
+        <v>-268.1376998305156</v>
       </c>
       <c r="Q69">
-        <v>-77.54038071536098</v>
+        <v>-81.93769983051561</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2011230874918381</v>
+        <v>0.2059769339759581</v>
       </c>
       <c r="T69">
-        <v>2.402798764837478</v>
+        <v>2.477886226238649</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02096256879786862</v>
+        <v>0.02065429572731173</v>
       </c>
       <c r="W69">
-        <v>0.2308570262774626</v>
+        <v>0.2309297170674999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1048128439893432</v>
+        <v>0.1032714786365587</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2229448264782065</v>
+        <v>0.2248448264782065</v>
       </c>
       <c r="C70">
-        <v>-473.5889825078775</v>
+        <v>-503.2982055762093</v>
       </c>
       <c r="D70">
-        <v>637.6345322849322</v>
+        <v>631.2359491400241</v>
       </c>
       <c r="E70">
-        <v>-200.1404775495575</v>
+        <v>-176.8298376261339</v>
       </c>
       <c r="F70">
-        <v>1585.12351479281</v>
+        <v>1608.434154716233</v>
       </c>
       <c r="G70">
         <v>473.9</v>
@@ -7027,37 +7027,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M70">
-        <v>373.7721247881445</v>
+        <v>379.2687736820878</v>
       </c>
       <c r="N70">
-        <v>-335.1721247881445</v>
+        <v>-340.6687736820878</v>
       </c>
       <c r="O70">
-        <v>-67.0344249576289</v>
+        <v>-68.13375473641757</v>
       </c>
       <c r="P70">
-        <v>-268.1376998305156</v>
+        <v>-272.5350189456702</v>
       </c>
       <c r="Q70">
-        <v>-81.93769983051561</v>
+        <v>-86.33501894567024</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2059769339759581</v>
+        <v>0.2111439318461503</v>
       </c>
       <c r="T70">
-        <v>2.477886226238649</v>
+        <v>2.557818039988283</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02065429572731173</v>
+        <v>0.02035495810807533</v>
       </c>
       <c r="W70">
-        <v>0.2309297170674999</v>
+        <v>0.2310003008781158</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1032714786365587</v>
+        <v>0.1017747905403767</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2248448264782065</v>
+        <v>0.2267448264782065</v>
       </c>
       <c r="C71">
-        <v>-503.2982055762093</v>
+        <v>-532.8802865293871</v>
       </c>
       <c r="D71">
-        <v>631.2359491400241</v>
+        <v>624.9645081102698</v>
       </c>
       <c r="E71">
-        <v>-176.8298376261339</v>
+        <v>-153.5191977027102</v>
       </c>
       <c r="F71">
-        <v>1608.434154716233</v>
+        <v>1631.744794639657</v>
       </c>
       <c r="G71">
         <v>473.9</v>
@@ -7109,37 +7109,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M71">
-        <v>379.2687736820878</v>
+        <v>384.7654225760311</v>
       </c>
       <c r="N71">
-        <v>-340.6687736820878</v>
+        <v>-346.1654225760311</v>
       </c>
       <c r="O71">
-        <v>-68.13375473641757</v>
+        <v>-69.23308451520623</v>
       </c>
       <c r="P71">
-        <v>-272.5350189456702</v>
+        <v>-276.9323380608249</v>
       </c>
       <c r="Q71">
-        <v>-86.33501894567024</v>
+        <v>-90.73233806082493</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2111439318461503</v>
+        <v>0.216655396241022</v>
       </c>
       <c r="T71">
-        <v>2.557818039988283</v>
+        <v>2.643078641321226</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02035495810807533</v>
+        <v>0.02006417299224568</v>
       </c>
       <c r="W71">
-        <v>0.2310003008781158</v>
+        <v>0.2310688680084285</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1017747905403767</v>
+        <v>0.1003208649612283</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2267448264782065</v>
+        <v>0.2286448264782065</v>
       </c>
       <c r="C72">
-        <v>-532.8802865293871</v>
+        <v>-562.3389776263971</v>
       </c>
       <c r="D72">
-        <v>624.9645081102698</v>
+        <v>618.8164569366835</v>
       </c>
       <c r="E72">
-        <v>-153.5191977027102</v>
+        <v>-130.2085577792866</v>
       </c>
       <c r="F72">
-        <v>1631.744794639657</v>
+        <v>1655.055434563081</v>
       </c>
       <c r="G72">
         <v>473.9</v>
@@ -7191,37 +7191,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M72">
-        <v>384.7654225760311</v>
+        <v>390.2620714699744</v>
       </c>
       <c r="N72">
-        <v>-346.1654225760311</v>
+        <v>-351.6620714699744</v>
       </c>
       <c r="O72">
-        <v>-69.23308451520623</v>
+        <v>-70.33241429399489</v>
       </c>
       <c r="P72">
-        <v>-276.9323380608249</v>
+        <v>-281.3296571759795</v>
       </c>
       <c r="Q72">
-        <v>-90.73233806082493</v>
+        <v>-95.12965717597956</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.216655396241022</v>
+        <v>0.2225469616286434</v>
       </c>
       <c r="T72">
-        <v>2.643078641321226</v>
+        <v>2.734219284125407</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02006417299224568</v>
+        <v>0.0197815790064394</v>
       </c>
       <c r="W72">
-        <v>0.2310688680084285</v>
+        <v>0.2311355036702816</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1003208649612283</v>
+        <v>0.09890789503219699</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2286448264782065</v>
+        <v>0.2305448264782065</v>
       </c>
       <c r="C73">
-        <v>-562.3389776263969</v>
+        <v>-591.677884914078</v>
       </c>
       <c r="D73">
-        <v>618.8164569366835</v>
+        <v>612.7881895724258</v>
       </c>
       <c r="E73">
-        <v>-130.2085577792868</v>
+        <v>-106.8979178558632</v>
       </c>
       <c r="F73">
-        <v>1655.05543456308</v>
+        <v>1678.366074486504</v>
       </c>
       <c r="G73">
         <v>473.9</v>
@@ -7273,37 +7273,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M73">
-        <v>390.2620714699743</v>
+        <v>395.7587203639176</v>
       </c>
       <c r="N73">
-        <v>-351.6620714699743</v>
+        <v>-357.1587203639176</v>
       </c>
       <c r="O73">
-        <v>-70.33241429399486</v>
+        <v>-71.43174407278353</v>
       </c>
       <c r="P73">
-        <v>-281.3296571759794</v>
+        <v>-285.7269762911341</v>
       </c>
       <c r="Q73">
-        <v>-95.12965717597945</v>
+        <v>-99.52697629113408</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2225469616286433</v>
+        <v>0.2288593531153806</v>
       </c>
       <c r="T73">
-        <v>2.734219284125405</v>
+        <v>2.83186997284417</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01978157900643941</v>
+        <v>0.01950683485357219</v>
       </c>
       <c r="W73">
-        <v>0.2311355036702816</v>
+        <v>0.2312002883415277</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0989078950321971</v>
+        <v>0.09753417426786104</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2305448264782065</v>
+        <v>0.2324448264782065</v>
       </c>
       <c r="C74">
-        <v>-591.677884914078</v>
+        <v>-620.9004752801254</v>
       </c>
       <c r="D74">
-        <v>612.7881895724258</v>
+        <v>606.8762391298023</v>
       </c>
       <c r="E74">
-        <v>-106.8979178558632</v>
+        <v>-83.58727793243929</v>
       </c>
       <c r="F74">
-        <v>1678.366074486504</v>
+        <v>1701.676714409928</v>
       </c>
       <c r="G74">
         <v>473.9</v>
@@ -7355,37 +7355,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M74">
-        <v>395.7587203639176</v>
+        <v>401.255369257861</v>
       </c>
       <c r="N74">
-        <v>-357.1587203639176</v>
+        <v>-362.655369257861</v>
       </c>
       <c r="O74">
-        <v>-71.43174407278353</v>
+        <v>-72.5310738515722</v>
       </c>
       <c r="P74">
-        <v>-285.7269762911341</v>
+        <v>-290.1242954062888</v>
       </c>
       <c r="Q74">
-        <v>-99.52697629113408</v>
+        <v>-103.9242954062888</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2288593531153806</v>
+        <v>0.235639329156691</v>
       </c>
       <c r="T74">
-        <v>2.83186997284417</v>
+        <v>2.936754045912473</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01950683485357219</v>
+        <v>0.01923961793776983</v>
       </c>
       <c r="W74">
-        <v>0.2312002883415277</v>
+        <v>0.2312632980902739</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09753417426786104</v>
+        <v>0.09619808968884913</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2324448264782065</v>
+        <v>0.2343448264782065</v>
       </c>
       <c r="C75">
-        <v>-620.9004752801254</v>
+        <v>-650.0100831017203</v>
       </c>
       <c r="D75">
-        <v>606.8762391298023</v>
+        <v>601.0772712316312</v>
       </c>
       <c r="E75">
-        <v>-83.58727793243929</v>
+        <v>-60.27663800901564</v>
       </c>
       <c r="F75">
-        <v>1701.676714409928</v>
+        <v>1724.987354333352</v>
       </c>
       <c r="G75">
         <v>473.9</v>
@@ -7437,37 +7437,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M75">
-        <v>401.255369257861</v>
+        <v>406.7520181518043</v>
       </c>
       <c r="N75">
-        <v>-362.655369257861</v>
+        <v>-368.1520181518043</v>
       </c>
       <c r="O75">
-        <v>-72.5310738515722</v>
+        <v>-73.63040363036087</v>
       </c>
       <c r="P75">
-        <v>-290.1242954062888</v>
+        <v>-294.5216145214434</v>
       </c>
       <c r="Q75">
-        <v>-103.9242954062888</v>
+        <v>-108.3216145214435</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.235639329156691</v>
+        <v>0.2429408418165637</v>
       </c>
       <c r="T75">
-        <v>2.936754045912473</v>
+        <v>3.049706124601414</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01923961793776983</v>
+        <v>0.01897962310077294</v>
       </c>
       <c r="W75">
-        <v>0.2312632980902739</v>
+        <v>0.2313246048728377</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09619808968884913</v>
+        <v>0.09489811550386462</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2343448264782065</v>
+        <v>0.2362448264782065</v>
       </c>
       <c r="C76">
-        <v>-650.0100831017203</v>
+        <v>-679.0099165165875</v>
       </c>
       <c r="D76">
-        <v>601.0772712316312</v>
+        <v>595.3880777401877</v>
       </c>
       <c r="E76">
-        <v>-60.27663800901564</v>
+        <v>-36.96599808559199</v>
       </c>
       <c r="F76">
-        <v>1724.987354333352</v>
+        <v>1748.297994256775</v>
       </c>
       <c r="G76">
         <v>473.9</v>
@@ -7519,37 +7519,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M76">
-        <v>406.7520181518043</v>
+        <v>412.2486670457476</v>
       </c>
       <c r="N76">
-        <v>-368.1520181518043</v>
+        <v>-373.6486670457476</v>
       </c>
       <c r="O76">
-        <v>-73.63040363036087</v>
+        <v>-74.72973340914953</v>
       </c>
       <c r="P76">
-        <v>-294.5216145214434</v>
+        <v>-298.9189336365981</v>
       </c>
       <c r="Q76">
-        <v>-108.3216145214435</v>
+        <v>-112.7189336365981</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2429408418165637</v>
+        <v>0.2508264754892263</v>
       </c>
       <c r="T76">
-        <v>3.049706124601414</v>
+        <v>3.17169436958547</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01897962310077294</v>
+        <v>0.0187265614594293</v>
       </c>
       <c r="W76">
-        <v>0.2313246048728377</v>
+        <v>0.2313842768078666</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09489811550386462</v>
+        <v>0.0936328072971464</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2362448264782065</v>
+        <v>0.2381448264782065</v>
       </c>
       <c r="C77">
-        <v>-679.0099165165875</v>
+        <v>-707.9030633412594</v>
       </c>
       <c r="D77">
-        <v>595.3880777401877</v>
+        <v>589.8055708389394</v>
       </c>
       <c r="E77">
-        <v>-36.96599808559199</v>
+        <v>-13.65535816216834</v>
       </c>
       <c r="F77">
-        <v>1748.297994256775</v>
+        <v>1771.608634180199</v>
       </c>
       <c r="G77">
         <v>473.9</v>
@@ -7601,37 +7601,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M77">
-        <v>412.2486670457476</v>
+        <v>417.7453159396909</v>
       </c>
       <c r="N77">
-        <v>-373.6486670457476</v>
+        <v>-379.1453159396909</v>
       </c>
       <c r="O77">
-        <v>-74.72973340914953</v>
+        <v>-75.82906318793819</v>
       </c>
       <c r="P77">
-        <v>-298.9189336365981</v>
+        <v>-303.3162527517528</v>
       </c>
       <c r="Q77">
-        <v>-112.7189336365981</v>
+        <v>-117.1162527517528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2508264754892263</v>
+        <v>0.2593692453012774</v>
       </c>
       <c r="T77">
-        <v>3.17169436958547</v>
+        <v>3.303848301651531</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0187265614594293</v>
+        <v>0.01848015933496313</v>
       </c>
       <c r="W77">
-        <v>0.2313842768078666</v>
+        <v>0.2314423784288157</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0936328072971464</v>
+        <v>0.0924007966748156</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2381448264782065</v>
+        <v>0.2400448264782065</v>
       </c>
       <c r="C78">
-        <v>-707.9030633412594</v>
+        <v>-736.692496659484</v>
       </c>
       <c r="D78">
-        <v>589.8055708389394</v>
+        <v>584.3267774441383</v>
       </c>
       <c r="E78">
-        <v>-13.65535816216834</v>
+        <v>9.65528176125531</v>
       </c>
       <c r="F78">
-        <v>1771.608634180199</v>
+        <v>1794.919274103622</v>
       </c>
       <c r="G78">
         <v>473.9</v>
@@ -7683,37 +7683,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M78">
-        <v>417.7453159396909</v>
+        <v>423.2419648336342</v>
       </c>
       <c r="N78">
-        <v>-379.1453159396909</v>
+        <v>-384.6419648336342</v>
       </c>
       <c r="O78">
-        <v>-75.82906318793819</v>
+        <v>-76.92839296672685</v>
       </c>
       <c r="P78">
-        <v>-303.3162527517528</v>
+        <v>-307.7135718669074</v>
       </c>
       <c r="Q78">
-        <v>-117.1162527517528</v>
+        <v>-121.5135718669074</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2593692453012774</v>
+        <v>0.2686548646622025</v>
       </c>
       <c r="T78">
-        <v>3.303848301651531</v>
+        <v>3.447493879984207</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01848015933496313</v>
+        <v>0.01824015726567789</v>
       </c>
       <c r="W78">
-        <v>0.2314423784288157</v>
+        <v>0.2314989709167532</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0924007966748156</v>
+        <v>0.09120078632838935</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2400448264782065</v>
+        <v>0.2419448264782065</v>
       </c>
       <c r="C79">
-        <v>-736.692496659484</v>
+        <v>-765.3810801020311</v>
       </c>
       <c r="D79">
-        <v>584.3267774441383</v>
+        <v>578.9488339250152</v>
       </c>
       <c r="E79">
-        <v>9.65528176125531</v>
+        <v>32.96592168467919</v>
       </c>
       <c r="F79">
-        <v>1794.919274103622</v>
+        <v>1818.229914027046</v>
       </c>
       <c r="G79">
         <v>473.9</v>
@@ -7765,37 +7765,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M79">
-        <v>423.2419648336342</v>
+        <v>428.7386137275776</v>
       </c>
       <c r="N79">
-        <v>-384.6419648336342</v>
+        <v>-390.1386137275775</v>
       </c>
       <c r="O79">
-        <v>-76.92839296672685</v>
+        <v>-78.02772274551552</v>
       </c>
       <c r="P79">
-        <v>-307.7135718669074</v>
+        <v>-312.110890982062</v>
       </c>
       <c r="Q79">
-        <v>-121.5135718669074</v>
+        <v>-125.910890982062</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2686548646622025</v>
+        <v>0.2787846312377572</v>
       </c>
       <c r="T79">
-        <v>3.447493879984207</v>
+        <v>3.604198147256217</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01824015726567789</v>
+        <v>0.01800630909560509</v>
       </c>
       <c r="W79">
-        <v>0.2314989709167532</v>
+        <v>0.2315541123152563</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09120078632838935</v>
+        <v>0.0900315454780255</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2419448264782065</v>
+        <v>0.2438448264782065</v>
       </c>
       <c r="C80">
-        <v>-765.3810801020311</v>
+        <v>-793.9715728375963</v>
       </c>
       <c r="D80">
-        <v>578.9488339250152</v>
+        <v>573.6689811128738</v>
       </c>
       <c r="E80">
-        <v>32.96592168467919</v>
+        <v>56.27656160810284</v>
       </c>
       <c r="F80">
-        <v>1818.229914027046</v>
+        <v>1841.54055395047</v>
       </c>
       <c r="G80">
         <v>473.9</v>
@@ -7847,37 +7847,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M80">
-        <v>428.7386137275776</v>
+        <v>434.2352626215209</v>
       </c>
       <c r="N80">
-        <v>-390.1386137275775</v>
+        <v>-395.6352626215208</v>
       </c>
       <c r="O80">
-        <v>-78.02772274551552</v>
+        <v>-79.12705252430418</v>
       </c>
       <c r="P80">
-        <v>-312.110890982062</v>
+        <v>-316.5082100972166</v>
       </c>
       <c r="Q80">
-        <v>-125.910890982062</v>
+        <v>-130.3082100972167</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2787846312377572</v>
+        <v>0.2898791374871742</v>
       </c>
       <c r="T80">
-        <v>3.604198147256217</v>
+        <v>3.775826630458894</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01800630909560509</v>
+        <v>0.01777838113236959</v>
       </c>
       <c r="W80">
-        <v>0.2315541123152563</v>
+        <v>0.2316078577289873</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0900315454780255</v>
+        <v>0.08889190566184801</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2438448264782065</v>
+        <v>0.2457448264782065</v>
       </c>
       <c r="C81">
-        <v>-793.9715728375963</v>
+        <v>-822.4666342930798</v>
       </c>
       <c r="D81">
-        <v>573.6689811128738</v>
+        <v>568.484559580814</v>
       </c>
       <c r="E81">
-        <v>56.27656160810284</v>
+        <v>79.58720153152649</v>
       </c>
       <c r="F81">
-        <v>1841.54055395047</v>
+        <v>1864.851193873894</v>
       </c>
       <c r="G81">
         <v>473.9</v>
@@ -7929,37 +7929,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M81">
-        <v>434.2352626215209</v>
+        <v>439.7319115154642</v>
       </c>
       <c r="N81">
-        <v>-395.6352626215208</v>
+        <v>-401.1319115154641</v>
       </c>
       <c r="O81">
-        <v>-79.12705252430418</v>
+        <v>-80.22638230309283</v>
       </c>
       <c r="P81">
-        <v>-316.5082100972166</v>
+        <v>-320.9055292123713</v>
       </c>
       <c r="Q81">
-        <v>-130.3082100972167</v>
+        <v>-134.7055292123713</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2898791374871742</v>
+        <v>0.3020830943615329</v>
       </c>
       <c r="T81">
-        <v>3.775826630458894</v>
+        <v>3.964617961981839</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01777838113236959</v>
+        <v>0.01755615136821497</v>
       </c>
       <c r="W81">
-        <v>0.2316078577289873</v>
+        <v>0.2316602595073749</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08889190566184801</v>
+        <v>0.08778075684107489</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2457448264782065</v>
+        <v>0.2476448264782065</v>
       </c>
       <c r="C82">
-        <v>-822.4666342930798</v>
+        <v>-850.8688286202046</v>
       </c>
       <c r="D82">
-        <v>568.484559580814</v>
+        <v>563.3930051771126</v>
       </c>
       <c r="E82">
-        <v>79.58720153152649</v>
+        <v>102.8978414549501</v>
       </c>
       <c r="F82">
-        <v>1864.851193873894</v>
+        <v>1888.161833797317</v>
       </c>
       <c r="G82">
         <v>473.9</v>
@@ -8011,37 +8011,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M82">
-        <v>439.7319115154642</v>
+        <v>445.2285604094074</v>
       </c>
       <c r="N82">
-        <v>-401.1319115154641</v>
+        <v>-406.6285604094074</v>
       </c>
       <c r="O82">
-        <v>-80.22638230309283</v>
+        <v>-81.32571208188149</v>
       </c>
       <c r="P82">
-        <v>-320.9055292123713</v>
+        <v>-325.302848327526</v>
       </c>
       <c r="Q82">
-        <v>-134.7055292123713</v>
+        <v>-139.102848327526</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3020830943615329</v>
+        <v>0.3155716782752979</v>
       </c>
       <c r="T82">
-        <v>3.964617961981839</v>
+        <v>4.173282065244042</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01755615136821497</v>
+        <v>0.01733940875873084</v>
       </c>
       <c r="W82">
-        <v>0.2316602595073749</v>
+        <v>0.2317113674146913</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08778075684107489</v>
+        <v>0.08669704379365406</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2476448264782065</v>
+        <v>0.2495448264782065</v>
       </c>
       <c r="C83">
-        <v>-850.8688286202046</v>
+        <v>-879.1806289242393</v>
       </c>
       <c r="D83">
-        <v>563.3930051771126</v>
+        <v>558.3918447965017</v>
       </c>
       <c r="E83">
-        <v>102.8978414549501</v>
+        <v>126.2084813783738</v>
       </c>
       <c r="F83">
-        <v>1888.161833797317</v>
+        <v>1911.472473720741</v>
       </c>
       <c r="G83">
         <v>473.9</v>
@@ -8093,37 +8093,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M83">
-        <v>445.2285604094074</v>
+        <v>450.7252093033507</v>
       </c>
       <c r="N83">
-        <v>-406.6285604094074</v>
+        <v>-412.1252093033507</v>
       </c>
       <c r="O83">
-        <v>-81.32571208188149</v>
+        <v>-82.42504186067015</v>
       </c>
       <c r="P83">
-        <v>-325.302848327526</v>
+        <v>-329.7001674426806</v>
       </c>
       <c r="Q83">
-        <v>-139.102848327526</v>
+        <v>-143.5001674426806</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3155716782752979</v>
+        <v>0.3305589937350366</v>
       </c>
       <c r="T83">
-        <v>4.173282065244042</v>
+        <v>4.40513106886871</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01733940875873084</v>
+        <v>0.01712795255435607</v>
       </c>
       <c r="W83">
-        <v>0.2317113674146913</v>
+        <v>0.2317612287876828</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08669704379365406</v>
+        <v>0.08563976277178031</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2495448264782065</v>
+        <v>0.2514448264782065</v>
       </c>
       <c r="C84">
-        <v>-879.1806289242393</v>
+        <v>-907.4044212694726</v>
       </c>
       <c r="D84">
-        <v>558.3918447965017</v>
+        <v>553.4786923746921</v>
       </c>
       <c r="E84">
-        <v>126.2084813783738</v>
+        <v>149.5191213017974</v>
       </c>
       <c r="F84">
-        <v>1911.472473720741</v>
+        <v>1934.783113644165</v>
       </c>
       <c r="G84">
         <v>473.9</v>
@@ -8175,37 +8175,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M84">
-        <v>450.7252093033507</v>
+        <v>456.221858197294</v>
       </c>
       <c r="N84">
-        <v>-412.1252093033507</v>
+        <v>-417.621858197294</v>
       </c>
       <c r="O84">
-        <v>-82.42504186067015</v>
+        <v>-83.52437163945882</v>
       </c>
       <c r="P84">
-        <v>-329.7001674426806</v>
+        <v>-334.0974865578352</v>
       </c>
       <c r="Q84">
-        <v>-143.5001674426806</v>
+        <v>-147.8974865578352</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3305589937350366</v>
+        <v>0.3473095227782741</v>
       </c>
       <c r="T84">
-        <v>4.40513106886871</v>
+        <v>4.664256425860988</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01712795255435607</v>
+        <v>0.0169215916802072</v>
       </c>
       <c r="W84">
-        <v>0.2317612287876828</v>
+        <v>0.2318098886818071</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08563976277178031</v>
+        <v>0.08460795840103597</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2514448264782065</v>
+        <v>0.2533448264782066</v>
       </c>
       <c r="C85">
-        <v>-907.4044212694726</v>
+        <v>-935.5425084750779</v>
       </c>
       <c r="D85">
-        <v>553.4786923746921</v>
+        <v>548.6512450925106</v>
       </c>
       <c r="E85">
-        <v>149.5191213017974</v>
+        <v>172.8297612252213</v>
       </c>
       <c r="F85">
-        <v>1934.783113644165</v>
+        <v>1958.093753567588</v>
       </c>
       <c r="G85">
         <v>473.9</v>
@@ -8257,37 +8257,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M85">
-        <v>456.221858197294</v>
+        <v>461.7185070912374</v>
       </c>
       <c r="N85">
-        <v>-417.621858197294</v>
+        <v>-423.1185070912373</v>
       </c>
       <c r="O85">
-        <v>-83.52437163945882</v>
+        <v>-84.62370141824748</v>
       </c>
       <c r="P85">
-        <v>-334.0974865578352</v>
+        <v>-338.4948056729899</v>
       </c>
       <c r="Q85">
-        <v>-147.8974865578352</v>
+        <v>-152.2948056729899</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3473095227782741</v>
+        <v>0.3661538679519163</v>
       </c>
       <c r="T85">
-        <v>4.664256425860988</v>
+        <v>4.955772452477301</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0169215916802072</v>
+        <v>0.01672014416020473</v>
       </c>
       <c r="W85">
-        <v>0.2318098886818071</v>
+        <v>0.2318573900070237</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08460795840103597</v>
+        <v>0.08360072080102376</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2533448264782065</v>
+        <v>0.2552448264782065</v>
       </c>
       <c r="C86">
-        <v>-935.5425084750774</v>
+        <v>-963.5971137140451</v>
       </c>
       <c r="D86">
-        <v>548.6512450925106</v>
+        <v>543.9072797769668</v>
       </c>
       <c r="E86">
-        <v>172.8297612252209</v>
+        <v>196.1404011486447</v>
       </c>
       <c r="F86">
-        <v>1958.093753567588</v>
+        <v>1981.404393491012</v>
       </c>
       <c r="G86">
         <v>473.9</v>
@@ -8339,37 +8339,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M86">
-        <v>461.7185070912373</v>
+        <v>467.2151559851806</v>
       </c>
       <c r="N86">
-        <v>-423.1185070912372</v>
+        <v>-428.6151559851806</v>
       </c>
       <c r="O86">
-        <v>-84.62370141824745</v>
+        <v>-85.72303119703614</v>
       </c>
       <c r="P86">
-        <v>-338.4948056729898</v>
+        <v>-342.8921247881445</v>
       </c>
       <c r="Q86">
-        <v>-152.2948056729898</v>
+        <v>-156.6921247881446</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.366153867951916</v>
+        <v>0.3875107924820438</v>
       </c>
       <c r="T86">
-        <v>4.955772452477297</v>
+        <v>5.28615728264245</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01672014416020473</v>
+        <v>0.01652343658184938</v>
       </c>
       <c r="W86">
-        <v>0.2318573900070237</v>
+        <v>0.2319037736539999</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08360072080102376</v>
+        <v>0.0826171829092468</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2552448264782065</v>
+        <v>0.2571448264782065</v>
       </c>
       <c r="C87">
-        <v>-963.5971137140451</v>
+        <v>-991.5703839270062</v>
       </c>
       <c r="D87">
-        <v>543.9072797769668</v>
+        <v>539.2446494874293</v>
       </c>
       <c r="E87">
-        <v>196.1404011486447</v>
+        <v>219.4510410720684</v>
       </c>
       <c r="F87">
-        <v>1981.404393491012</v>
+        <v>2004.715033414436</v>
       </c>
       <c r="G87">
         <v>473.9</v>
@@ -8421,37 +8421,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M87">
-        <v>467.2151559851806</v>
+        <v>472.7118048791239</v>
       </c>
       <c r="N87">
-        <v>-428.6151559851806</v>
+        <v>-434.111804879124</v>
       </c>
       <c r="O87">
-        <v>-85.72303119703614</v>
+        <v>-86.82236097582479</v>
       </c>
       <c r="P87">
-        <v>-342.8921247881445</v>
+        <v>-347.2894439032992</v>
       </c>
       <c r="Q87">
-        <v>-156.6921247881446</v>
+        <v>-161.0894439032992</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3875107924820438</v>
+        <v>0.4119187062307613</v>
       </c>
       <c r="T87">
-        <v>5.28615728264245</v>
+        <v>5.663739945688341</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01652343658184938</v>
+        <v>0.0163313035983395</v>
       </c>
       <c r="W87">
-        <v>0.2319037736539999</v>
+        <v>0.2319490786115116</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.0826171829092468</v>
+        <v>0.08165651799169749</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2571448264782065</v>
+        <v>0.2590448264782065</v>
       </c>
       <c r="C88">
-        <v>-991.5703839270062</v>
+        <v>-1019.464393061961</v>
       </c>
       <c r="D88">
-        <v>539.2446494874293</v>
+        <v>534.6612802758981</v>
       </c>
       <c r="E88">
-        <v>219.4510410720684</v>
+        <v>242.761680995492</v>
       </c>
       <c r="F88">
-        <v>2004.715033414436</v>
+        <v>2028.025673337859</v>
       </c>
       <c r="G88">
         <v>473.9</v>
@@ -8503,37 +8503,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M88">
-        <v>472.7118048791239</v>
+        <v>478.2084537730672</v>
       </c>
       <c r="N88">
-        <v>-434.111804879124</v>
+        <v>-439.6084537730673</v>
       </c>
       <c r="O88">
-        <v>-86.82236097582479</v>
+        <v>-87.92169075461345</v>
       </c>
       <c r="P88">
-        <v>-347.2894439032992</v>
+        <v>-351.6867630184538</v>
       </c>
       <c r="Q88">
-        <v>-161.0894439032992</v>
+        <v>-165.4867630184538</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4119187062307613</v>
+        <v>0.4400816836331274</v>
       </c>
       <c r="T88">
-        <v>5.663739945688341</v>
+        <v>6.099412249202827</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0163313035983395</v>
+        <v>0.01614358746502526</v>
       </c>
       <c r="W88">
-        <v>0.2319490786115116</v>
+        <v>0.231993342075747</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08165651799169749</v>
+        <v>0.08071793732512622</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2590448264782065</v>
+        <v>0.2609448264782065</v>
       </c>
       <c r="C89">
-        <v>-1019.464393061961</v>
+        <v>-1047.281145150178</v>
       </c>
       <c r="D89">
-        <v>534.6612802758981</v>
+        <v>530.1551681111056</v>
       </c>
       <c r="E89">
-        <v>242.761680995492</v>
+        <v>266.0723209189159</v>
       </c>
       <c r="F89">
-        <v>2028.025673337859</v>
+        <v>2051.336313261283</v>
       </c>
       <c r="G89">
         <v>473.9</v>
@@ -8585,37 +8585,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M89">
-        <v>478.2084537730672</v>
+        <v>483.7051026670106</v>
       </c>
       <c r="N89">
-        <v>-439.6084537730673</v>
+        <v>-445.1051026670106</v>
       </c>
       <c r="O89">
-        <v>-87.92169075461345</v>
+        <v>-89.02102053340212</v>
       </c>
       <c r="P89">
-        <v>-351.6867630184538</v>
+        <v>-356.0840821336084</v>
       </c>
       <c r="Q89">
-        <v>-165.4867630184538</v>
+        <v>-169.8840821336084</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4400816836331274</v>
+        <v>0.4729384906025548</v>
       </c>
       <c r="T89">
-        <v>6.099412249202827</v>
+        <v>6.607696603303064</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01614358746502526</v>
+        <v>0.01596013760746815</v>
       </c>
       <c r="W89">
-        <v>0.231993342075747</v>
+        <v>0.232036599552159</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08071793732512622</v>
+        <v>0.07980068803734086</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2609448264782065</v>
+        <v>0.2628448264782065</v>
       </c>
       <c r="C90">
-        <v>-1047.281145150178</v>
+        <v>-1075.02257722785</v>
       </c>
       <c r="D90">
-        <v>530.1551681111056</v>
+        <v>525.7243759568568</v>
       </c>
       <c r="E90">
-        <v>266.0723209189159</v>
+        <v>289.3829608423393</v>
       </c>
       <c r="F90">
-        <v>2051.336313261283</v>
+        <v>2074.646953184706</v>
       </c>
       <c r="G90">
         <v>473.9</v>
@@ -8667,37 +8667,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M90">
-        <v>483.7051026670106</v>
+        <v>489.2017515609538</v>
       </c>
       <c r="N90">
-        <v>-445.1051026670106</v>
+        <v>-450.6017515609539</v>
       </c>
       <c r="O90">
-        <v>-89.02102053340212</v>
+        <v>-90.12035031219078</v>
       </c>
       <c r="P90">
-        <v>-356.0840821336084</v>
+        <v>-360.4814012487631</v>
       </c>
       <c r="Q90">
-        <v>-169.8840821336084</v>
+        <v>-174.2814012487631</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4729384906025548</v>
+        <v>0.5117692624755144</v>
       </c>
       <c r="T90">
-        <v>6.607696603303064</v>
+        <v>7.208396294512434</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01596013760746815</v>
+        <v>0.0157808102186202</v>
       </c>
       <c r="W90">
-        <v>0.232036599552159</v>
+        <v>0.2320788849504494</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07980068803734086</v>
+        <v>0.07890405109310095</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2628448264782065</v>
+        <v>0.2647448264782065</v>
       </c>
       <c r="C91">
-        <v>-1075.02257722785</v>
+        <v>-1102.690562112467</v>
       </c>
       <c r="D91">
-        <v>525.7243759568568</v>
+        <v>521.3670309956633</v>
       </c>
       <c r="E91">
-        <v>289.3829608423393</v>
+        <v>312.6936007657632</v>
       </c>
       <c r="F91">
-        <v>2074.646953184706</v>
+        <v>2097.95759310813</v>
       </c>
       <c r="G91">
         <v>473.9</v>
@@ -8749,37 +8749,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M91">
-        <v>489.2017515609538</v>
+        <v>494.6984004548972</v>
       </c>
       <c r="N91">
-        <v>-450.6017515609539</v>
+        <v>-456.0984004548972</v>
       </c>
       <c r="O91">
-        <v>-90.12035031219078</v>
+        <v>-91.21968009097944</v>
       </c>
       <c r="P91">
-        <v>-360.4814012487631</v>
+        <v>-364.8787203639178</v>
       </c>
       <c r="Q91">
-        <v>-174.2814012487631</v>
+        <v>-178.6787203639178</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5117692624755144</v>
+        <v>0.5583661887230658</v>
       </c>
       <c r="T91">
-        <v>7.208396294512434</v>
+        <v>7.929235923963677</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0157808102186202</v>
+        <v>0.01560546788285775</v>
       </c>
       <c r="W91">
-        <v>0.2320788849504494</v>
+        <v>0.2321202306732222</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07890405109310095</v>
+        <v>0.07802733941428874</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2647448264782065</v>
+        <v>0.2666448264782065</v>
       </c>
       <c r="C92">
-        <v>-1102.690562112467</v>
+        <v>-1130.286911042243</v>
       </c>
       <c r="D92">
-        <v>521.3670309956633</v>
+        <v>517.0813219893107</v>
       </c>
       <c r="E92">
-        <v>312.6936007657632</v>
+        <v>336.0042406891866</v>
       </c>
       <c r="F92">
-        <v>2097.95759310813</v>
+        <v>2121.268233031554</v>
       </c>
       <c r="G92">
         <v>473.9</v>
@@ -8831,37 +8831,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M92">
-        <v>494.6984004548972</v>
+        <v>500.1950493488404</v>
       </c>
       <c r="N92">
-        <v>-456.0984004548972</v>
+        <v>-461.5950493488405</v>
       </c>
       <c r="O92">
-        <v>-91.21968009097944</v>
+        <v>-92.3190098697681</v>
       </c>
       <c r="P92">
-        <v>-364.8787203639178</v>
+        <v>-369.2760394790724</v>
       </c>
       <c r="Q92">
-        <v>-178.6787203639178</v>
+        <v>-183.0760394790724</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5583661887230658</v>
+        <v>0.615317987470073</v>
       </c>
       <c r="T92">
-        <v>7.929235923963677</v>
+        <v>8.81026213773742</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01560546788285775</v>
+        <v>0.01543397922480437</v>
       </c>
       <c r="W92">
-        <v>0.2321202306732222</v>
+        <v>0.2321606676987911</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07802733941428874</v>
+        <v>0.07716989612402181</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2666448264782065</v>
+        <v>0.2685448264782065</v>
       </c>
       <c r="C93">
-        <v>-1130.286911042243</v>
+        <v>-1157.813376186435</v>
       </c>
       <c r="D93">
-        <v>517.0813219893107</v>
+        <v>512.8654967685426</v>
       </c>
       <c r="E93">
-        <v>336.0042406891866</v>
+        <v>359.3148806126105</v>
       </c>
       <c r="F93">
-        <v>2121.268233031554</v>
+        <v>2144.578872954978</v>
       </c>
       <c r="G93">
         <v>473.9</v>
@@ -8913,37 +8913,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M93">
-        <v>500.1950493488404</v>
+        <v>505.6916982427837</v>
       </c>
       <c r="N93">
-        <v>-461.5950493488405</v>
+        <v>-467.0916982427838</v>
       </c>
       <c r="O93">
-        <v>-92.3190098697681</v>
+        <v>-93.41833964855675</v>
       </c>
       <c r="P93">
-        <v>-369.2760394790724</v>
+        <v>-373.673358594227</v>
       </c>
       <c r="Q93">
-        <v>-183.0760394790724</v>
+        <v>-187.473358594227</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.615317987470073</v>
+        <v>0.6865077359038325</v>
       </c>
       <c r="T93">
-        <v>8.81026213773742</v>
+        <v>9.911544904954601</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01543397922480437</v>
+        <v>0.0152662185810565</v>
       </c>
       <c r="W93">
-        <v>0.2321606676987911</v>
+        <v>0.2322002256585869</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07716989612402181</v>
+        <v>0.07633109290528239</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2685448264782065</v>
+        <v>0.2704448264782065</v>
       </c>
       <c r="C94">
-        <v>-1157.813376186435</v>
+        <v>-1185.271653033847</v>
       </c>
       <c r="D94">
-        <v>512.8654967685426</v>
+        <v>508.717859844554</v>
       </c>
       <c r="E94">
-        <v>359.3148806126105</v>
+        <v>382.6255205360339</v>
       </c>
       <c r="F94">
-        <v>2144.578872954978</v>
+        <v>2167.889512878401</v>
       </c>
       <c r="G94">
         <v>473.9</v>
@@ -8995,37 +8995,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M94">
-        <v>505.6916982427837</v>
+        <v>511.188347136727</v>
       </c>
       <c r="N94">
-        <v>-467.0916982427838</v>
+        <v>-472.588347136727</v>
       </c>
       <c r="O94">
-        <v>-93.41833964855675</v>
+        <v>-94.5176694273454</v>
       </c>
       <c r="P94">
-        <v>-373.673358594227</v>
+        <v>-378.0706777093816</v>
       </c>
       <c r="Q94">
-        <v>-187.473358594227</v>
+        <v>-191.8706777093816</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6865077359038325</v>
+        <v>0.7780374124615229</v>
       </c>
       <c r="T94">
-        <v>9.911544904954601</v>
+        <v>11.32747989137669</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0152662185810565</v>
+        <v>0.01510206569308815</v>
       </c>
       <c r="W94">
-        <v>0.2322002256585869</v>
+        <v>0.2322389329095698</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07633109290528239</v>
+        <v>0.07551032846544081</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2704448264782065</v>
+        <v>0.2723448264782065</v>
       </c>
       <c r="C95">
-        <v>-1185.271653033847</v>
+        <v>-1212.663382666374</v>
       </c>
       <c r="D95">
-        <v>508.717859844554</v>
+        <v>504.6367701354508</v>
       </c>
       <c r="E95">
-        <v>382.6255205360339</v>
+        <v>405.9361604594578</v>
       </c>
       <c r="F95">
-        <v>2167.889512878401</v>
+        <v>2191.200152801825</v>
       </c>
       <c r="G95">
         <v>473.9</v>
@@ -9077,37 +9077,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M95">
-        <v>511.188347136727</v>
+        <v>516.6849960306704</v>
       </c>
       <c r="N95">
-        <v>-472.588347136727</v>
+        <v>-478.0849960306704</v>
       </c>
       <c r="O95">
-        <v>-94.5176694273454</v>
+        <v>-95.61699920613408</v>
       </c>
       <c r="P95">
-        <v>-378.0706777093816</v>
+        <v>-382.4679968245363</v>
       </c>
       <c r="Q95">
-        <v>-191.8706777093816</v>
+        <v>-196.2679968245363</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7780374124615229</v>
+        <v>0.9000769812051104</v>
       </c>
       <c r="T95">
-        <v>11.32747989137669</v>
+        <v>13.21539320660614</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01510206569308815</v>
+        <v>0.01494140541975742</v>
       </c>
       <c r="W95">
-        <v>0.2322389329095698</v>
+        <v>0.2322768166020212</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07551032846544081</v>
+        <v>0.07470702709878718</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2723448264782065</v>
+        <v>0.2742448264782065</v>
       </c>
       <c r="C96">
-        <v>-1212.663382666374</v>
+        <v>-1239.990153923974</v>
       </c>
       <c r="D96">
-        <v>504.6367701354508</v>
+        <v>500.6206388012749</v>
       </c>
       <c r="E96">
-        <v>405.9361604594578</v>
+        <v>429.2468003828817</v>
       </c>
       <c r="F96">
-        <v>2191.200152801825</v>
+        <v>2214.510792725249</v>
       </c>
       <c r="G96">
         <v>473.9</v>
@@ -9159,37 +9159,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M96">
-        <v>516.6849960306704</v>
+        <v>522.1816449246137</v>
       </c>
       <c r="N96">
-        <v>-478.0849960306704</v>
+        <v>-483.5816449246137</v>
       </c>
       <c r="O96">
-        <v>-95.61699920613408</v>
+        <v>-96.71632898492274</v>
       </c>
       <c r="P96">
-        <v>-382.4679968245363</v>
+        <v>-386.865315939691</v>
       </c>
       <c r="Q96">
-        <v>-196.2679968245363</v>
+        <v>-200.665315939691</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9000769812051104</v>
+        <v>1.070932377446133</v>
       </c>
       <c r="T96">
-        <v>13.21539320660614</v>
+        <v>15.85847184792738</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01494140541975742</v>
+        <v>0.0147841274679705</v>
       </c>
       <c r="W96">
-        <v>0.2322768166020212</v>
+        <v>0.2323139027430526</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07470702709878718</v>
+        <v>0.07392063733985255</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2742448264782065</v>
+        <v>0.2761448264782065</v>
       </c>
       <c r="C97">
-        <v>-1239.990153923974</v>
+        <v>-1267.253505467081</v>
       </c>
       <c r="D97">
-        <v>500.6206388012749</v>
+        <v>496.667927181591</v>
       </c>
       <c r="E97">
-        <v>429.2468003828817</v>
+        <v>452.5574403063051</v>
       </c>
       <c r="F97">
-        <v>2214.510792725249</v>
+        <v>2237.821432648672</v>
       </c>
       <c r="G97">
         <v>473.9</v>
@@ -9241,37 +9241,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M97">
-        <v>522.1816449246137</v>
+        <v>527.678293818557</v>
       </c>
       <c r="N97">
-        <v>-483.5816449246137</v>
+        <v>-489.078293818557</v>
       </c>
       <c r="O97">
-        <v>-96.71632898492274</v>
+        <v>-97.8156587637114</v>
       </c>
       <c r="P97">
-        <v>-386.865315939691</v>
+        <v>-391.2626350548456</v>
       </c>
       <c r="Q97">
-        <v>-200.665315939691</v>
+        <v>-205.0626350548456</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.070932377446133</v>
+        <v>1.327215471807667</v>
       </c>
       <c r="T97">
-        <v>15.85847184792738</v>
+        <v>19.82308980990923</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0147841274679705</v>
+        <v>0.01463012614017914</v>
       </c>
       <c r="W97">
-        <v>0.2323139027430526</v>
+        <v>0.2323502162561458</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07392063733985255</v>
+        <v>0.07315063070089578</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2761448264782065</v>
+        <v>0.2780448264782065</v>
       </c>
       <c r="C98">
-        <v>-1267.253505467081</v>
+        <v>-1294.454927742084</v>
       </c>
       <c r="D98">
-        <v>496.6679271815912</v>
+        <v>492.777144830012</v>
       </c>
       <c r="E98">
-        <v>452.5574403063051</v>
+        <v>475.8680802297285</v>
       </c>
       <c r="F98">
-        <v>2237.821432648672</v>
+        <v>2261.132072572096</v>
       </c>
       <c r="G98">
         <v>473.9</v>
@@ -9323,37 +9323,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M98">
-        <v>527.678293818557</v>
+        <v>533.1749427125002</v>
       </c>
       <c r="N98">
-        <v>-489.078293818557</v>
+        <v>-494.5749427125002</v>
       </c>
       <c r="O98">
-        <v>-97.8156587637114</v>
+        <v>-98.91498854250004</v>
       </c>
       <c r="P98">
-        <v>-391.2626350548456</v>
+        <v>-395.6599541700001</v>
       </c>
       <c r="Q98">
-        <v>-205.0626350548456</v>
+        <v>-209.4599541700001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.327215471807663</v>
+        <v>1.754353962410218</v>
       </c>
       <c r="T98">
-        <v>19.82308980990917</v>
+        <v>26.43078641321224</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01463012614017914</v>
+        <v>0.01447930009749688</v>
       </c>
       <c r="W98">
-        <v>0.2323502162561458</v>
+        <v>0.2323857810370102</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07315063070089578</v>
+        <v>0.07239650048748447</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2780448264782065</v>
+        <v>0.2799448264782065</v>
       </c>
       <c r="C99">
-        <v>-1294.454927742084</v>
+        <v>-1321.59586485513</v>
       </c>
       <c r="D99">
-        <v>492.777144830012</v>
+        <v>488.9468476403892</v>
       </c>
       <c r="E99">
-        <v>475.8680802297285</v>
+        <v>499.1787201531524</v>
       </c>
       <c r="F99">
-        <v>2261.132072572096</v>
+        <v>2284.44271249552</v>
       </c>
       <c r="G99">
         <v>473.9</v>
@@ -9405,37 +9405,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M99">
-        <v>533.1749427125002</v>
+        <v>538.6715916064435</v>
       </c>
       <c r="N99">
-        <v>-494.5749427125002</v>
+        <v>-500.0715916064435</v>
       </c>
       <c r="O99">
-        <v>-98.91498854250004</v>
+        <v>-100.0143183212887</v>
       </c>
       <c r="P99">
-        <v>-395.6599541700001</v>
+        <v>-400.0572732851548</v>
       </c>
       <c r="Q99">
-        <v>-209.4599541700001</v>
+        <v>-213.8572732851548</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.754353962410218</v>
+        <v>2.608630943615326</v>
       </c>
       <c r="T99">
-        <v>26.43078641321224</v>
+        <v>39.64617961981835</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01447930009749688</v>
+        <v>0.01433155213731834</v>
       </c>
       <c r="W99">
-        <v>0.2323857810370102</v>
+        <v>0.2324206200060203</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07239650048748447</v>
+        <v>0.0716577606865918</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2799448264782065</v>
+        <v>0.2818448264782065</v>
       </c>
       <c r="C100">
-        <v>-1321.59586485513</v>
+        <v>-1348.677716359225</v>
       </c>
       <c r="D100">
-        <v>488.9468476403892</v>
+        <v>485.1756360597179</v>
       </c>
       <c r="E100">
-        <v>499.1787201531524</v>
+        <v>522.4893600765758</v>
       </c>
       <c r="F100">
-        <v>2284.44271249552</v>
+        <v>2307.753352418943</v>
       </c>
       <c r="G100">
         <v>473.9</v>
@@ -9487,37 +9487,37 @@
         <v>38.59999999999999</v>
       </c>
       <c r="M100">
-        <v>538.6715916064435</v>
+        <v>544.1682405003868</v>
       </c>
       <c r="N100">
-        <v>-500.0715916064435</v>
+        <v>-505.5682405003868</v>
       </c>
       <c r="O100">
-        <v>-100.0143183212887</v>
+        <v>-101.1136481000774</v>
       </c>
       <c r="P100">
-        <v>-400.0572732851548</v>
+        <v>-404.4545924003094</v>
       </c>
       <c r="Q100">
-        <v>-213.8572732851548</v>
+        <v>-218.2545924003094</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.608630943615326</v>
+        <v>5.171461887230652</v>
       </c>
       <c r="T100">
-        <v>39.64617961981835</v>
+        <v>79.2923592396367</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01433155213731834</v>
+        <v>0.01418678898441614</v>
       </c>
       <c r="W100">
-        <v>0.2324206200060203</v>
+        <v>0.2324547551574747</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0716577606865918</v>
+        <v>0.07093394492208072</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2818448264782065</v>
-      </c>
-      <c r="C101">
-        <v>-1348.677716359225</v>
-      </c>
-      <c r="D101">
-        <v>485.1756360597179</v>
-      </c>
-      <c r="E101">
-        <v>522.4893600765758</v>
-      </c>
-      <c r="F101">
-        <v>2307.753352418943</v>
-      </c>
-      <c r="G101">
-        <v>473.9</v>
-      </c>
-      <c r="H101">
-        <v>545.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>224.8</v>
-      </c>
-      <c r="K101">
-        <v>186.2</v>
-      </c>
-      <c r="L101">
-        <v>38.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>544.1682405003868</v>
-      </c>
-      <c r="N101">
-        <v>-505.5682405003868</v>
-      </c>
-      <c r="O101">
-        <v>-101.1136481000774</v>
-      </c>
-      <c r="P101">
-        <v>-404.4545924003094</v>
-      </c>
-      <c r="Q101">
-        <v>-218.2545924003094</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.171461887230652</v>
-      </c>
-      <c r="T101">
-        <v>79.2923592396367</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01418678898441614</v>
-      </c>
-      <c r="W101">
-        <v>0.2324547551574747</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07093394492208072</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
